--- a/summary_files/data_summary.xlsx
+++ b/summary_files/data_summary.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\01eco\Desktop\UoGuelph\multisource_ML_research\summary_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\01eco\Documents\Programming\Python\multisource_ML_research\summary_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78ED6E8-5289-43F7-8923-F0A91B5382F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFE645E-3784-4976-883C-8BF2A6F700B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="DataInfo" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$Y$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$Z$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="180">
   <si>
     <t>Eye tracking? (Y/N)</t>
   </si>
@@ -75,9 +75,6 @@
     <t>LastDrove</t>
   </si>
   <si>
-    <t>DrivingFrequency</t>
-  </si>
-  <si>
     <t>DrivingTypicalLength</t>
   </si>
   <si>
@@ -108,33 +105,36 @@
     <t>HalfSig</t>
   </si>
   <si>
+    <t>ltmajor_collision</t>
+  </si>
+  <si>
+    <t>ltsig_collision</t>
+  </si>
+  <si>
+    <t>ltminor_collision</t>
+  </si>
+  <si>
+    <t>lthalf_collision</t>
+  </si>
+  <si>
     <t>Looking Away From Mirror (s) (Tobii)</t>
   </si>
   <si>
     <t>Looking Away From Mirror (s) (SCANeR Recording)</t>
   </si>
   <si>
-    <t>Time Difference</t>
-  </si>
-  <si>
     <t>Notes:</t>
   </si>
   <si>
-    <t xml:space="preserve">G </t>
+    <t>G</t>
   </si>
   <si>
     <t xml:space="preserve">More than 1 week ago </t>
   </si>
   <si>
-    <t xml:space="preserve">6-20 times per month </t>
-  </si>
-  <si>
     <t xml:space="preserve">Between 15 and 30 minutes </t>
   </si>
   <si>
-    <t xml:space="preserve">Urban </t>
-  </si>
-  <si>
     <t xml:space="preserve">High school diploma </t>
   </si>
   <si>
@@ -156,9 +156,6 @@
     <t xml:space="preserve">Within the last 24 hours </t>
   </si>
   <si>
-    <t xml:space="preserve">21-60 times per month </t>
-  </si>
-  <si>
     <t xml:space="preserve">Less than 15 minutes </t>
   </si>
   <si>
@@ -183,9 +180,6 @@
     <t>Within the last week</t>
   </si>
   <si>
-    <t>6-20 times per month</t>
-  </si>
-  <si>
     <t>Between 15 and 30 minutes</t>
   </si>
   <si>
@@ -207,15 +201,6 @@
     <t>went through yellow, accelerated, near miss</t>
   </si>
   <si>
-    <t xml:space="preserve">G2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">More than 60 times per month </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highway </t>
-  </si>
-  <si>
     <t xml:space="preserve">went through yellow, near miss, no collision </t>
   </si>
   <si>
@@ -255,15 +240,9 @@
     <t>stopped and waited for hazard, no collision</t>
   </si>
   <si>
-    <t>G</t>
-  </si>
-  <si>
     <t>Within the last 24 hours</t>
   </si>
   <si>
-    <t>More than 60 times per month</t>
-  </si>
-  <si>
     <t>Rural</t>
   </si>
   <si>
@@ -294,18 +273,9 @@
     <t xml:space="preserve">Between 30 minutes and 1 hour </t>
   </si>
   <si>
-    <t xml:space="preserve">Rural </t>
-  </si>
-  <si>
     <t>Accelerated through yellow, no collision</t>
   </si>
   <si>
-    <t>accelerated through yellow, near miss</t>
-  </si>
-  <si>
-    <t>battery died during drive (1 hazard recorded LT Major). Eye Tracking ends early</t>
-  </si>
-  <si>
     <t>Went through yellow, accelerated, swerved, collision</t>
   </si>
   <si>
@@ -348,18 +318,12 @@
     <t>Mentioned she has a lazy eye</t>
   </si>
   <si>
-    <t xml:space="preserve">0-5 times per month </t>
-  </si>
-  <si>
     <t>braked to avoid collision, then went through yellow</t>
   </si>
   <si>
     <t>Went through yellow, near miss</t>
   </si>
   <si>
-    <t>21-60 times per month</t>
-  </si>
-  <si>
     <t>Undergraduate Diploma</t>
   </si>
   <si>
@@ -381,15 +345,9 @@
     <t>went through yellow, near miss</t>
   </si>
   <si>
-    <t>0-5 times per month</t>
-  </si>
-  <si>
     <t>Ran yellow, near miss, no collision</t>
   </si>
   <si>
-    <t>0-5 times a month</t>
-  </si>
-  <si>
     <t>Highschool diploma</t>
   </si>
   <si>
@@ -549,9 +507,6 @@
     <t>went though yellow, near miss</t>
   </si>
   <si>
-    <t xml:space="preserve">Female </t>
-  </si>
-  <si>
     <t>Stopped for hazard, reversed to stop bar, no collision</t>
   </si>
   <si>
@@ -603,16 +558,25 @@
     <t>Did not stop,  swerved, no collision</t>
   </si>
   <si>
-    <t>ltmajor_collision</t>
-  </si>
-  <si>
-    <t>ltsig_collision</t>
-  </si>
-  <si>
-    <t>ltminor_collision</t>
-  </si>
-  <si>
-    <t>lthalf_collision</t>
+    <t>MonthlyDrivingFrequency</t>
+  </si>
+  <si>
+    <t>(6-20)</t>
+  </si>
+  <si>
+    <t>(21-60)</t>
+  </si>
+  <si>
+    <t>(60+)</t>
+  </si>
+  <si>
+    <t>(0-5)</t>
+  </si>
+  <si>
+    <t>DrivingExperience</t>
+  </si>
+  <si>
+    <t>TimeDifferenceEtoD</t>
   </si>
 </sst>
 </file>
@@ -686,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -733,6 +697,9 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -754,11 +721,36 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -772,9 +764,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AA74" totalsRowShown="0">
-  <autoFilter ref="A1:AA74" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AB71" totalsRowShown="0">
+  <autoFilter ref="A1:AB71" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Order"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="HazardOrder"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="participant_id"/>
@@ -782,11 +774,14 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="AgeStart"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Licence"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="LastDrove"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="DrivingFrequency"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="MonthlyDrivingFrequency" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DrivingTypicalLength"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="AvgKM"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Type"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="CurrentAge"/>
+    <tableColumn id="28" xr3:uid="{D2E7A76E-A255-4531-A907-C2950F0B6E7A}" name="DrivingExperience" dataDxfId="0">
+      <calculatedColumnFormula>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Education"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Gender"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Tmaj"/>
@@ -800,9 +795,7 @@
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Eye tracking? (Y/N)"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Looking Away From Mirror (s) (Tobii)"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Looking Away From Mirror (s) (SCANeR Recording)"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Time Difference">
-      <calculatedColumnFormula>X2-Y2</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="TimeDifferenceEtoD"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Notes:"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1097,35 +1090,36 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AA80"/>
+  <dimension ref="A1:AB77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.28515625" style="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="21" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" hidden="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="33" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="15.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.42578125" style="22" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.28515625" style="22" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.85546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="35.28515625" style="20" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="47.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="21" customWidth="1"/>
+    <col min="14" max="14" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="15.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.85546875" style="20" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="35.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="47.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="26.140625" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -1148,67 +1142,70 @@
         <v>11</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="P1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="S1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="T1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>189</v>
-      </c>
       <c r="U1" s="8" t="s">
-        <v>190</v>
+        <v>23</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>44</v>
       </c>
@@ -1225,71 +1222,75 @@
         <v>16</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" s="10">
         <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L2" s="10">
         <v>21</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>5</v>
+      </c>
+      <c r="N2" t="s">
         <v>32</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="P2" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="Q2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="R2" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="S2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="14">
+      <c r="T2" s="14">
         <v>-1</v>
       </c>
-      <c r="T2" s="15">
-        <v>1</v>
-      </c>
       <c r="U2" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="15">
         <v>0</v>
       </c>
-      <c r="W2" s="9">
-        <v>1</v>
-      </c>
-      <c r="X2" s="10">
+      <c r="W2" s="15">
+        <v>0</v>
+      </c>
+      <c r="X2" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="10">
         <v>7</v>
       </c>
-      <c r="Y2" s="10">
+      <c r="Z2" s="10">
         <v>6</v>
       </c>
-      <c r="Z2" s="10">
-        <f>X2-Y2</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA2" s="10">
+        <f t="shared" ref="AA2:AA33" si="0">Y2-Z2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>59</v>
       </c>
@@ -1306,47 +1307,48 @@
         <v>16</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I3" t="s">
         <v>39</v>
-      </c>
-      <c r="I3" t="s">
-        <v>40</v>
       </c>
       <c r="J3" s="10">
         <v>5</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L3" s="10">
         <v>57</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
         <v>41</v>
       </c>
       <c r="N3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="P3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="R3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="S3" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" s="15">
-        <v>0</v>
-      </c>
       <c r="T3" s="15">
         <v>0</v>
       </c>
@@ -1354,23 +1356,26 @@
         <v>0</v>
       </c>
       <c r="V3" s="15">
-        <v>1</v>
-      </c>
-      <c r="W3" s="9">
-        <v>1</v>
-      </c>
-      <c r="X3" s="10">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="W3" s="15">
+        <v>1</v>
+      </c>
+      <c r="X3" s="9">
+        <v>1</v>
       </c>
       <c r="Y3" s="10">
         <v>8</v>
       </c>
       <c r="Z3" s="10">
-        <f t="shared" ref="Z3:Z66" si="0">X3-Y3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="AA3" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>74</v>
       </c>
@@ -1387,71 +1392,75 @@
         <v>16</v>
       </c>
       <c r="F4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
         <v>46</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4" t="s">
         <v>47</v>
-      </c>
-      <c r="H4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" t="s">
-        <v>49</v>
       </c>
       <c r="J4" s="10">
         <v>30</v>
       </c>
       <c r="K4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L4" s="10">
         <v>19</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
+      </c>
+      <c r="N4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="13" t="s">
+      <c r="R4" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="S4" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="S4" s="15">
-        <v>0</v>
-      </c>
       <c r="T4" s="15">
         <v>0</v>
       </c>
       <c r="U4" s="15">
+        <v>0</v>
+      </c>
+      <c r="V4" s="15">
         <v>2</v>
       </c>
-      <c r="V4" s="15">
-        <v>1</v>
-      </c>
-      <c r="W4" s="9">
-        <v>1</v>
-      </c>
-      <c r="X4" s="10">
+      <c r="W4" s="15">
+        <v>1</v>
+      </c>
+      <c r="X4" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="10">
         <v>5</v>
       </c>
-      <c r="Y4" s="10">
+      <c r="Z4" s="10">
         <v>7</v>
       </c>
-      <c r="Z4" s="10">
+      <c r="AA4" s="10">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>26</v>
       </c>
@@ -1468,46 +1477,47 @@
         <v>16</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G5" t="s">
         <v>38</v>
       </c>
-      <c r="H5" t="s">
-        <v>57</v>
+      <c r="H5" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J5" s="10">
         <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="L5" s="10">
         <v>19</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
+      </c>
+      <c r="N5" t="s">
         <v>32</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="13" t="s">
-        <v>44</v>
-      </c>
       <c r="P5" s="13" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="Q5" s="13" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="S5" s="15">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="S5" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="T5" s="15">
         <v>0</v>
@@ -1516,23 +1526,26 @@
         <v>0</v>
       </c>
       <c r="V5" s="15">
-        <v>1</v>
-      </c>
-      <c r="W5" s="9">
-        <v>1</v>
-      </c>
-      <c r="X5" s="10">
+        <v>0</v>
+      </c>
+      <c r="W5" s="15">
+        <v>1</v>
+      </c>
+      <c r="X5" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="10">
         <v>5</v>
       </c>
-      <c r="Y5" s="10">
+      <c r="Z5" s="10">
         <v>6</v>
       </c>
-      <c r="Z5" s="10">
+      <c r="AA5" s="10">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>56</v>
       </c>
@@ -1549,71 +1562,75 @@
         <v>16</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
         <v>38</v>
       </c>
-      <c r="H6" t="s">
-        <v>57</v>
+      <c r="H6" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" s="10">
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L6" s="10">
         <v>58</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>42</v>
+      </c>
+      <c r="N6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q6" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="S6" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="N6" t="s">
-        <v>62</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="P6" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="R6" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="S6" s="15">
-        <v>0</v>
-      </c>
       <c r="T6" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="15">
-        <v>1</v>
-      </c>
-      <c r="W6" s="9">
-        <v>1</v>
-      </c>
-      <c r="X6" s="10">
+        <v>0</v>
+      </c>
+      <c r="W6" s="15">
+        <v>1</v>
+      </c>
+      <c r="X6" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="10">
         <v>6</v>
       </c>
-      <c r="Y6" s="10">
+      <c r="Z6" s="10">
         <v>5</v>
       </c>
-      <c r="Z6" s="10">
+      <c r="AA6" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>55</v>
       </c>
@@ -1630,46 +1647,47 @@
         <v>16</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" t="s">
-        <v>29</v>
+        <v>62</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7" s="10">
         <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L7" s="10">
         <v>55</v>
       </c>
-      <c r="M7" t="s">
-        <v>68</v>
+      <c r="M7" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>62</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="O7" t="s">
+        <v>57</v>
       </c>
       <c r="P7" s="13" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="R7" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="S7" s="15">
-        <v>0</v>
+      <c r="S7" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="T7" s="15">
         <v>0</v>
@@ -1678,23 +1696,26 @@
         <v>0</v>
       </c>
       <c r="V7" s="15">
-        <v>1</v>
-      </c>
-      <c r="W7" s="9">
-        <v>1</v>
-      </c>
-      <c r="X7" s="10">
+        <v>0</v>
+      </c>
+      <c r="W7" s="15">
+        <v>1</v>
+      </c>
+      <c r="X7" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="10">
         <v>8</v>
       </c>
-      <c r="Y7" s="10">
+      <c r="Z7" s="10">
         <v>5</v>
       </c>
-      <c r="Z7" s="10">
+      <c r="AA7" s="10">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>17</v>
       </c>
@@ -1711,71 +1732,75 @@
         <v>16</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J8" s="10">
         <v>50</v>
       </c>
       <c r="K8" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L8" s="10">
         <v>51</v>
       </c>
-      <c r="M8" t="s">
-        <v>76</v>
+      <c r="M8" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>35</v>
       </c>
       <c r="N8" t="s">
-        <v>62</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>44</v>
+        <v>69</v>
+      </c>
+      <c r="O8" t="s">
+        <v>57</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="Q8" s="13" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S8" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T8" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="15">
         <v>0</v>
       </c>
-      <c r="W8" s="9">
-        <v>1</v>
-      </c>
-      <c r="X8" s="10">
+      <c r="W8" s="15">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="10">
         <v>5</v>
       </c>
-      <c r="Y8" s="9">
+      <c r="Z8" s="9">
         <v>7</v>
       </c>
-      <c r="Z8" s="10">
+      <c r="AA8" s="10">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>54</v>
       </c>
@@ -1792,46 +1817,47 @@
         <v>16</v>
       </c>
       <c r="F9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" t="s">
         <v>46</v>
       </c>
-      <c r="G9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" t="s">
-        <v>48</v>
+      <c r="H9" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="J9" s="10">
         <v>50</v>
       </c>
       <c r="K9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L9" s="10">
         <v>17</v>
       </c>
-      <c r="M9" t="s">
-        <v>51</v>
+      <c r="M9" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>62</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>69</v>
+        <v>49</v>
+      </c>
+      <c r="O9" t="s">
+        <v>57</v>
       </c>
       <c r="P9" s="13" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="S9" s="15">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="S9" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="T9" s="15">
         <v>0</v>
@@ -1840,23 +1866,26 @@
         <v>0</v>
       </c>
       <c r="V9" s="15">
-        <v>1</v>
-      </c>
-      <c r="W9" s="9">
-        <v>1</v>
-      </c>
-      <c r="X9" s="10">
+        <v>0</v>
+      </c>
+      <c r="W9" s="15">
+        <v>1</v>
+      </c>
+      <c r="X9" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="10">
         <v>6</v>
       </c>
-      <c r="Y9" s="10">
+      <c r="Z9" s="10">
         <v>10</v>
       </c>
-      <c r="Z9" s="10">
+      <c r="AA9" s="10">
         <f t="shared" si="0"/>
         <v>-4</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>12</v>
       </c>
@@ -1873,151 +1902,160 @@
         <v>16</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="I10" t="s">
         <v>47</v>
-      </c>
-      <c r="H10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" t="s">
-        <v>49</v>
       </c>
       <c r="J10" s="10">
         <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L10" s="10">
         <v>21</v>
       </c>
-      <c r="M10" t="s">
-        <v>51</v>
+      <c r="M10" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>5</v>
       </c>
       <c r="N10" t="s">
+        <v>49</v>
+      </c>
+      <c r="O10" t="s">
         <v>33</v>
       </c>
-      <c r="O10" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="P10" s="13" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S10" s="15">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="S10" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T10" s="15">
+        <v>0</v>
+      </c>
+      <c r="U10" s="15">
         <v>2</v>
       </c>
-      <c r="U10" s="15">
-        <v>0</v>
-      </c>
       <c r="V10" s="15">
         <v>0</v>
       </c>
-      <c r="W10" s="9">
-        <v>1</v>
-      </c>
-      <c r="X10" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="9">
+      <c r="W10" s="15">
+        <v>0</v>
+      </c>
+      <c r="X10" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="9">
         <v>5</v>
       </c>
-      <c r="Z10" s="10">
+      <c r="AA10" s="10">
         <f t="shared" si="0"/>
         <v>-4</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="B11" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C11" s="9">
         <v>9</v>
       </c>
       <c r="D11" s="1">
-        <v>21051</v>
+        <v>97051</v>
       </c>
       <c r="E11" s="10">
         <v>16</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="G11" t="s">
         <v>38</v>
       </c>
-      <c r="H11" t="s">
-        <v>29</v>
+      <c r="H11" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="J11" s="10">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K11" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="L11" s="10">
-        <v>18</v>
-      </c>
-      <c r="M11" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="M11" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>8</v>
       </c>
       <c r="N11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="O11" t="s">
+        <v>57</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q11" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="R11" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="S11" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="P11" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q11" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="R11" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="S11" s="15">
-        <v>0</v>
-      </c>
       <c r="T11" s="15">
         <v>0</v>
       </c>
       <c r="U11" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="15">
-        <v>1</v>
-      </c>
-      <c r="W11" s="9">
-        <v>0</v>
-      </c>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="15">
+        <v>1</v>
+      </c>
+      <c r="X11" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="10">
+        <v>9</v>
+      </c>
       <c r="Z11" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="AA11" s="10">
+        <f>Y11-Z11</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>69</v>
       </c>
@@ -2034,46 +2072,47 @@
         <v>16</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" t="s">
-        <v>39</v>
+        <v>30</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J12" s="10">
         <v>10</v>
       </c>
       <c r="K12" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L12" s="10">
         <v>18</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>2</v>
+      </c>
+      <c r="N12" t="s">
         <v>32</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>33</v>
       </c>
-      <c r="O12" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="P12" s="13" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="S12" s="15">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="S12" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="T12" s="15">
         <v>0</v>
@@ -2082,23 +2121,26 @@
         <v>0</v>
       </c>
       <c r="V12" s="15">
+        <v>0</v>
+      </c>
+      <c r="W12" s="15">
         <v>2</v>
       </c>
-      <c r="W12" s="9">
-        <v>1</v>
-      </c>
-      <c r="X12" s="10">
+      <c r="X12" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="10">
         <v>7</v>
       </c>
-      <c r="Y12" s="10">
+      <c r="Z12" s="10">
         <v>6</v>
       </c>
-      <c r="Z12" s="10">
+      <c r="AA12" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>4</v>
       </c>
@@ -2115,46 +2157,47 @@
         <v>17</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
         <v>38</v>
       </c>
-      <c r="H13" t="s">
-        <v>39</v>
+      <c r="H13" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J13" s="10">
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L13" s="10">
         <v>20</v>
       </c>
-      <c r="M13" t="s">
-        <v>90</v>
+      <c r="M13" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
       </c>
       <c r="N13" t="s">
-        <v>62</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>44</v>
+        <v>80</v>
+      </c>
+      <c r="O13" t="s">
+        <v>57</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="S13" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S13" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="T13" s="15">
         <v>0</v>
@@ -2163,23 +2206,26 @@
         <v>0</v>
       </c>
       <c r="V13" s="15">
+        <v>0</v>
+      </c>
+      <c r="W13" s="15">
         <v>2</v>
       </c>
-      <c r="W13" s="9">
-        <v>1</v>
-      </c>
-      <c r="X13" s="10">
+      <c r="X13" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="10">
         <v>4</v>
       </c>
-      <c r="Y13" s="9">
+      <c r="Z13" s="9">
         <v>5</v>
       </c>
-      <c r="Z13" s="10">
+      <c r="AA13" s="10">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>49</v>
       </c>
@@ -2196,46 +2242,47 @@
         <v>16</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" t="s">
-        <v>48</v>
+        <v>82</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J14" s="10">
         <v>20</v>
       </c>
       <c r="K14" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L14" s="10">
         <v>19</v>
       </c>
-      <c r="M14" t="s">
-        <v>51</v>
+      <c r="M14" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
       </c>
       <c r="N14" t="s">
+        <v>49</v>
+      </c>
+      <c r="O14" t="s">
         <v>33</v>
       </c>
-      <c r="O14" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="P14" s="13" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="Q14" s="13" t="s">
         <v>71</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="S14" s="15">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="S14" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="T14" s="15">
         <v>0</v>
@@ -2244,26 +2291,29 @@
         <v>0</v>
       </c>
       <c r="V14" s="15">
-        <v>1</v>
-      </c>
-      <c r="W14" s="9">
-        <v>1</v>
-      </c>
-      <c r="X14" s="10">
+        <v>0</v>
+      </c>
+      <c r="W14" s="15">
+        <v>1</v>
+      </c>
+      <c r="X14" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="10">
         <v>7</v>
       </c>
-      <c r="Y14" s="10">
+      <c r="Z14" s="10">
         <v>12</v>
       </c>
-      <c r="Z14" s="10">
+      <c r="AA14" s="10">
         <f t="shared" si="0"/>
         <v>-5</v>
       </c>
-      <c r="AA14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB14" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>72</v>
       </c>
@@ -2280,46 +2330,47 @@
         <v>16</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G15" t="s">
         <v>38</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I15" t="s">
         <v>39</v>
-      </c>
-      <c r="I15" t="s">
-        <v>40</v>
       </c>
       <c r="J15" s="10">
         <v>6</v>
       </c>
       <c r="K15" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L15" s="10">
         <v>23</v>
       </c>
-      <c r="M15" t="s">
-        <v>68</v>
+      <c r="M15" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>7</v>
       </c>
       <c r="N15" t="s">
+        <v>63</v>
+      </c>
+      <c r="O15" t="s">
         <v>33</v>
       </c>
-      <c r="O15" s="13" t="s">
-        <v>96</v>
-      </c>
       <c r="P15" s="13" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="S15" s="15">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="S15" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="T15" s="15">
         <v>0</v>
@@ -2330,21 +2381,24 @@
       <c r="V15" s="15">
         <v>0</v>
       </c>
-      <c r="W15" s="9">
-        <v>1</v>
-      </c>
-      <c r="X15" s="10">
+      <c r="W15" s="15">
+        <v>0</v>
+      </c>
+      <c r="X15" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="10">
         <v>8</v>
       </c>
-      <c r="Y15" s="10">
+      <c r="Z15" s="10">
         <v>11</v>
       </c>
-      <c r="Z15" s="10">
+      <c r="AA15" s="10">
         <f t="shared" si="0"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>40</v>
       </c>
@@ -2361,49 +2415,50 @@
         <v>16</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
         <v>38</v>
       </c>
-      <c r="H16" t="s">
-        <v>29</v>
+      <c r="H16" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J16" s="10">
         <v>6</v>
       </c>
       <c r="K16" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L16" s="10">
         <v>18</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>2</v>
+      </c>
+      <c r="N16" t="s">
         <v>32</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>33</v>
       </c>
-      <c r="O16" s="13" t="s">
-        <v>98</v>
-      </c>
       <c r="P16" s="13" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="Q16" s="13" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S16" s="15">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="S16" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T16" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" s="15">
         <v>0</v>
@@ -2411,21 +2466,24 @@
       <c r="V16" s="15">
         <v>0</v>
       </c>
-      <c r="W16" s="9">
-        <v>1</v>
-      </c>
-      <c r="X16" s="10">
+      <c r="W16" s="15">
+        <v>0</v>
+      </c>
+      <c r="X16" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="10">
         <v>4</v>
       </c>
-      <c r="Y16" s="10">
+      <c r="Z16" s="10">
         <v>9</v>
       </c>
-      <c r="Z16" s="10">
+      <c r="AA16" s="10">
         <f t="shared" si="0"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>48</v>
       </c>
@@ -2442,46 +2500,47 @@
         <v>16</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" t="s">
-        <v>48</v>
+        <v>82</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J17" s="10">
         <v>5</v>
       </c>
       <c r="K17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L17" s="10">
         <v>19</v>
       </c>
-      <c r="M17" t="s">
-        <v>51</v>
+      <c r="M17" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
       </c>
       <c r="N17" t="s">
+        <v>49</v>
+      </c>
+      <c r="O17" t="s">
         <v>33</v>
       </c>
-      <c r="O17" s="13" t="s">
-        <v>100</v>
-      </c>
       <c r="P17" s="13" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="S17" s="15">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="S17" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="T17" s="15">
         <v>0</v>
@@ -2490,26 +2549,29 @@
         <v>0</v>
       </c>
       <c r="V17" s="15">
-        <v>1</v>
-      </c>
-      <c r="W17" s="9">
-        <v>1</v>
-      </c>
-      <c r="X17" s="10">
+        <v>0</v>
+      </c>
+      <c r="W17" s="15">
+        <v>1</v>
+      </c>
+      <c r="X17" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="10">
         <v>9</v>
       </c>
-      <c r="Y17" s="10">
+      <c r="Z17" s="10">
         <v>20</v>
       </c>
-      <c r="Z17" s="10">
+      <c r="AA17" s="10">
         <f t="shared" si="0"/>
         <v>-11</v>
       </c>
-      <c r="AA17" s="13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB17" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>64</v>
       </c>
@@ -2526,46 +2588,47 @@
         <v>16</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" t="s">
-        <v>103</v>
+        <v>30</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>177</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J18" s="10">
         <v>17</v>
       </c>
       <c r="K18" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="L18" s="10">
         <v>17</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>1</v>
+      </c>
+      <c r="N18" t="s">
         <v>32</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>33</v>
       </c>
-      <c r="O18" s="13" t="s">
-        <v>44</v>
-      </c>
       <c r="P18" s="13" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="R18" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="S18" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S18" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="T18" s="15">
         <v>0</v>
@@ -2574,23 +2637,26 @@
         <v>0</v>
       </c>
       <c r="V18" s="15">
-        <v>1</v>
-      </c>
-      <c r="W18" s="9">
-        <v>1</v>
-      </c>
-      <c r="X18" s="10">
+        <v>0</v>
+      </c>
+      <c r="W18" s="15">
+        <v>1</v>
+      </c>
+      <c r="X18" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="10">
         <v>9</v>
       </c>
-      <c r="Y18" s="10">
+      <c r="Z18" s="10">
         <v>6</v>
       </c>
-      <c r="Z18" s="10">
+      <c r="AA18" s="10">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>35</v>
       </c>
@@ -2607,71 +2673,75 @@
         <v>16</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G19" t="s">
         <v>38</v>
       </c>
-      <c r="H19" t="s">
-        <v>106</v>
+      <c r="H19" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J19" s="10">
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L19" s="10">
         <v>24</v>
       </c>
-      <c r="M19" t="s">
-        <v>107</v>
+      <c r="M19" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>8</v>
       </c>
       <c r="N19" t="s">
-        <v>62</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>44</v>
+        <v>95</v>
+      </c>
+      <c r="O19" t="s">
+        <v>57</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="S19" s="15">
-        <v>0</v>
+        <v>97</v>
+      </c>
+      <c r="S19" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="T19" s="15">
+        <v>0</v>
+      </c>
+      <c r="U19" s="15">
         <v>2</v>
       </c>
-      <c r="U19" s="15">
-        <v>0</v>
-      </c>
       <c r="V19" s="15">
         <v>0</v>
       </c>
-      <c r="W19" s="9">
-        <v>1</v>
-      </c>
-      <c r="X19" s="10">
+      <c r="W19" s="15">
+        <v>0</v>
+      </c>
+      <c r="X19" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="10">
         <v>7</v>
       </c>
-      <c r="Y19" s="10">
+      <c r="Z19" s="10">
         <v>11</v>
       </c>
-      <c r="Z19" s="10">
+      <c r="AA19" s="10">
         <f t="shared" si="0"/>
         <v>-4</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>28</v>
       </c>
@@ -2688,1128 +2758,1184 @@
         <v>16</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G20" t="s">
         <v>38</v>
       </c>
-      <c r="H20" t="s">
-        <v>103</v>
+      <c r="H20" s="24" t="s">
+        <v>177</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J20" s="10">
         <v>10</v>
       </c>
       <c r="K20" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L20" s="10">
         <v>19</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
+      </c>
+      <c r="N20" t="s">
         <v>32</v>
       </c>
-      <c r="N20" t="s">
-        <v>62</v>
-      </c>
-      <c r="O20" s="13" t="s">
-        <v>111</v>
+      <c r="O20" t="s">
+        <v>57</v>
       </c>
       <c r="P20" s="13" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="Q20" s="13" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="R20" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="S20" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S20" s="13" t="s">
+        <v>101</v>
       </c>
       <c r="T20" s="15">
+        <v>0</v>
+      </c>
+      <c r="U20" s="15">
         <v>2</v>
       </c>
-      <c r="U20" s="15">
-        <v>0</v>
-      </c>
       <c r="V20" s="15">
-        <v>1</v>
-      </c>
-      <c r="W20" s="9">
-        <v>1</v>
-      </c>
-      <c r="X20" s="10">
+        <v>0</v>
+      </c>
+      <c r="W20" s="15">
+        <v>1</v>
+      </c>
+      <c r="X20" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="10">
         <v>5</v>
       </c>
-      <c r="Y20" s="10">
+      <c r="Z20" s="10">
         <v>10</v>
       </c>
-      <c r="Z20" s="10">
+      <c r="AA20" s="10">
         <f t="shared" si="0"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="B21" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" s="9">
         <v>19</v>
       </c>
       <c r="D21" s="1">
-        <v>26585</v>
+        <v>97448</v>
       </c>
       <c r="E21" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" t="s">
-        <v>39</v>
+        <v>147</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I21" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="J21" s="10">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="K21" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L21" s="10">
         <v>18</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M21" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
         <v>32</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>33</v>
       </c>
-      <c r="O21" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="P21" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="S21" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="T21" s="15">
+        <v>0</v>
+      </c>
+      <c r="U21" s="15">
+        <v>0</v>
+      </c>
+      <c r="V21" s="15">
+        <v>0</v>
+      </c>
+      <c r="W21" s="15">
+        <v>0</v>
+      </c>
+      <c r="X21" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="10">
+        <v>6</v>
+      </c>
+      <c r="Z21" s="10">
+        <v>13</v>
+      </c>
+      <c r="AA21" s="10">
+        <f>Y21-Z21</f>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="9">
+        <v>1</v>
+      </c>
+      <c r="C22" s="9">
+        <v>20</v>
+      </c>
+      <c r="D22" s="1">
+        <v>28334</v>
+      </c>
+      <c r="E22" s="10">
+        <v>16</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="I22" t="s">
+        <v>83</v>
+      </c>
+      <c r="J22" s="10">
+        <v>8</v>
+      </c>
+      <c r="K22" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" s="10">
+        <v>21</v>
+      </c>
+      <c r="M22" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>5</v>
+      </c>
+      <c r="N22" t="s">
+        <v>49</v>
+      </c>
+      <c r="O22" t="s">
+        <v>57</v>
+      </c>
+      <c r="P22" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="S22" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="T22" s="15">
+        <v>0</v>
+      </c>
+      <c r="U22" s="15">
+        <v>0</v>
+      </c>
+      <c r="V22" s="15">
+        <v>0</v>
+      </c>
+      <c r="W22" s="15">
+        <v>0</v>
+      </c>
+      <c r="X22" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="10">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="9">
+        <v>9</v>
+      </c>
+      <c r="AA22" s="10">
+        <f t="shared" si="0"/>
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>41</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9">
+        <v>21</v>
+      </c>
+      <c r="D23" s="1">
+        <v>29048</v>
+      </c>
+      <c r="E23" s="10">
+        <v>16</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="I23" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="10">
+        <v>15</v>
+      </c>
+      <c r="K23" t="s">
+        <v>68</v>
+      </c>
+      <c r="L23" s="10">
+        <v>18</v>
+      </c>
+      <c r="M23" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>2</v>
+      </c>
+      <c r="N23" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="S23" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="T23" s="15">
+        <v>0</v>
+      </c>
+      <c r="U23" s="15">
+        <v>1</v>
+      </c>
+      <c r="V23" s="15">
+        <v>0</v>
+      </c>
+      <c r="W23" s="15">
+        <v>0</v>
+      </c>
+      <c r="X23" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="10">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="10">
+        <v>7</v>
+      </c>
+      <c r="AA23" s="10">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>63</v>
+      </c>
+      <c r="B24" s="9">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9">
+        <v>22</v>
+      </c>
+      <c r="D24" s="1">
+        <v>29097</v>
+      </c>
+      <c r="E24" s="10">
+        <v>16</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="I24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="10">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s">
+        <v>48</v>
+      </c>
+      <c r="L24" s="10">
+        <v>21</v>
+      </c>
+      <c r="M24" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>5</v>
+      </c>
+      <c r="N24" t="s">
+        <v>103</v>
+      </c>
+      <c r="O24" t="s">
+        <v>33</v>
+      </c>
+      <c r="P24" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q24" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="R24" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="S24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="T24" s="15">
+        <v>0</v>
+      </c>
+      <c r="U24" s="15">
+        <v>0</v>
+      </c>
+      <c r="V24" s="15">
+        <v>0</v>
+      </c>
+      <c r="W24" s="15">
+        <v>1</v>
+      </c>
+      <c r="X24" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="10">
+        <v>10</v>
+      </c>
+      <c r="Z24" s="10">
+        <v>8</v>
+      </c>
+      <c r="AA24" s="10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AB24" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>5</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9">
+        <v>23</v>
+      </c>
+      <c r="D25" s="1">
+        <v>34473</v>
+      </c>
+      <c r="E25" s="10">
+        <v>16</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J25" s="10">
+        <v>30</v>
+      </c>
+      <c r="K25" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="10">
+        <v>19</v>
+      </c>
+      <c r="M25" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
+      </c>
+      <c r="N25" t="s">
+        <v>32</v>
+      </c>
+      <c r="O25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P25" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q25" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="R25" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="S25" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="T25" s="15">
+        <v>0</v>
+      </c>
+      <c r="U25" s="15">
+        <v>0</v>
+      </c>
+      <c r="V25" s="15">
+        <v>0</v>
+      </c>
+      <c r="W25" s="15">
+        <v>1</v>
+      </c>
+      <c r="X25" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="9">
+        <v>5</v>
+      </c>
+      <c r="Z25" s="9">
+        <v>6</v>
+      </c>
+      <c r="AA25" s="10">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>21</v>
+      </c>
+      <c r="B26" s="9">
+        <v>2</v>
+      </c>
+      <c r="C26" s="9">
+        <v>24</v>
+      </c>
+      <c r="D26" s="1">
+        <v>35217</v>
+      </c>
+      <c r="E26" s="10">
+        <v>16</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="I26" t="s">
+        <v>72</v>
+      </c>
+      <c r="J26" s="10">
+        <v>60</v>
+      </c>
+      <c r="K26" t="s">
+        <v>68</v>
+      </c>
+      <c r="L26" s="10">
+        <v>21</v>
+      </c>
+      <c r="M26" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>5</v>
+      </c>
+      <c r="N26" t="s">
+        <v>49</v>
+      </c>
+      <c r="O26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q26" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="S26" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="T26" s="15">
+        <v>0</v>
+      </c>
+      <c r="U26" s="15">
+        <v>0</v>
+      </c>
+      <c r="V26" s="15">
+        <v>0</v>
+      </c>
+      <c r="W26" s="15">
+        <v>0</v>
+      </c>
+      <c r="X26" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="10">
+        <v>4</v>
+      </c>
+      <c r="Z26" s="10">
+        <v>8</v>
+      </c>
+      <c r="AA26" s="10">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>16</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0</v>
+      </c>
+      <c r="C27" s="9">
+        <v>25</v>
+      </c>
+      <c r="D27" s="1">
+        <v>35745</v>
+      </c>
+      <c r="E27" s="10">
+        <v>16</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" t="s">
+        <v>67</v>
+      </c>
+      <c r="H27" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="I27" t="s">
+        <v>47</v>
+      </c>
+      <c r="J27" s="10">
+        <v>20</v>
+      </c>
+      <c r="K27" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="10">
+        <v>49</v>
+      </c>
+      <c r="M27" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>33</v>
+      </c>
+      <c r="N27" t="s">
+        <v>95</v>
+      </c>
+      <c r="O27" t="s">
+        <v>33</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q27" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="R27" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="S27" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="T27" s="15">
+        <v>0</v>
+      </c>
+      <c r="U27" s="15">
+        <v>1</v>
+      </c>
+      <c r="V27" s="15">
+        <v>0</v>
+      </c>
+      <c r="W27" s="14">
+        <v>-1</v>
+      </c>
+      <c r="X27" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="10">
+        <v>2</v>
+      </c>
+      <c r="AA27" s="10">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>7</v>
+      </c>
+      <c r="B28" s="9">
+        <v>2</v>
+      </c>
+      <c r="C28" s="9">
+        <v>26</v>
+      </c>
+      <c r="D28" s="1">
+        <v>37883</v>
+      </c>
+      <c r="E28" s="10">
+        <v>16</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="I28" t="s">
+        <v>77</v>
+      </c>
+      <c r="J28" s="10">
+        <v>50</v>
+      </c>
+      <c r="K28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L28" s="10">
+        <v>19</v>
+      </c>
+      <c r="M28" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
+      </c>
+      <c r="N28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O28" t="s">
+        <v>57</v>
+      </c>
+      <c r="P28" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q28" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="R28" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="S28" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="T28" s="15">
+        <v>0</v>
+      </c>
+      <c r="U28" s="15">
+        <v>0</v>
+      </c>
+      <c r="V28" s="15">
+        <v>0</v>
+      </c>
+      <c r="W28" s="15">
+        <v>1</v>
+      </c>
+      <c r="X28" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="15">
+        <v>5</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="10">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="AB28" s="15"/>
+    </row>
+    <row r="29" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>73</v>
+      </c>
+      <c r="B29" s="9">
+        <v>3</v>
+      </c>
+      <c r="C29" s="9">
+        <v>27</v>
+      </c>
+      <c r="D29" s="1">
+        <v>38989</v>
+      </c>
+      <c r="E29" s="10">
+        <v>16</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" t="s">
+        <v>67</v>
+      </c>
+      <c r="H29" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I29" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="10">
+        <v>15</v>
+      </c>
+      <c r="K29" t="s">
+        <v>48</v>
+      </c>
+      <c r="L29" s="10">
+        <v>19</v>
+      </c>
+      <c r="M29" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
+      </c>
+      <c r="N29" t="s">
+        <v>112</v>
+      </c>
+      <c r="O29" t="s">
+        <v>33</v>
+      </c>
+      <c r="P29" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="Q21" s="13" t="s">
+      <c r="Q29" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="R21" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="S21" s="15">
-        <v>0</v>
-      </c>
-      <c r="T21" s="15">
-        <v>1</v>
-      </c>
-      <c r="U21" s="15">
-        <v>0</v>
-      </c>
-      <c r="V21" s="15">
-        <v>0</v>
-      </c>
-      <c r="W21" s="9">
-        <v>1</v>
-      </c>
-      <c r="X21" s="10">
-        <v>12</v>
-      </c>
-      <c r="Y21" s="10">
-        <v>15</v>
-      </c>
-      <c r="Z21" s="10">
+      <c r="R29" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="S29" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="T29" s="14">
+        <v>-1</v>
+      </c>
+      <c r="U29" s="15">
+        <v>0</v>
+      </c>
+      <c r="V29" s="15">
+        <v>0</v>
+      </c>
+      <c r="W29" s="15">
+        <v>2</v>
+      </c>
+      <c r="X29" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="10">
+        <v>4</v>
+      </c>
+      <c r="Z29" s="10">
+        <v>7</v>
+      </c>
+      <c r="AA29" s="10">
         <f t="shared" si="0"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" s="9">
-        <v>1</v>
-      </c>
-      <c r="C22" s="9">
-        <v>20</v>
-      </c>
-      <c r="D22" s="1">
-        <v>28334</v>
-      </c>
-      <c r="E22" s="10">
+    <row r="30" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>60</v>
+      </c>
+      <c r="B30" s="9">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9">
+        <v>28</v>
+      </c>
+      <c r="D30" s="1">
+        <v>39692</v>
+      </c>
+      <c r="E30" s="10">
+        <v>23</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I30" t="s">
+        <v>39</v>
+      </c>
+      <c r="J30" s="10">
+        <v>5</v>
+      </c>
+      <c r="K30" t="s">
+        <v>48</v>
+      </c>
+      <c r="L30" s="10">
+        <v>55</v>
+      </c>
+      <c r="M30" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>32</v>
+      </c>
+      <c r="N30" t="s">
+        <v>40</v>
+      </c>
+      <c r="O30" t="s">
+        <v>33</v>
+      </c>
+      <c r="P30" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q30" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="R30" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="S30" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="T30" s="15">
+        <v>0</v>
+      </c>
+      <c r="U30" s="15">
+        <v>1</v>
+      </c>
+      <c r="V30" s="15">
+        <v>0</v>
+      </c>
+      <c r="W30" s="15">
+        <v>0</v>
+      </c>
+      <c r="X30" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="10">
+        <v>12</v>
+      </c>
+      <c r="Z30" s="10">
+        <v>11</v>
+      </c>
+      <c r="AA30" s="10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>58</v>
+      </c>
+      <c r="B31" s="9">
+        <v>2</v>
+      </c>
+      <c r="C31" s="9">
+        <v>29</v>
+      </c>
+      <c r="D31" s="1">
+        <v>41473</v>
+      </c>
+      <c r="E31" s="10">
         <v>16</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
-      </c>
-      <c r="H22" t="s">
-        <v>114</v>
-      </c>
-      <c r="I22" t="s">
-        <v>93</v>
-      </c>
-      <c r="J22" s="10">
+      <c r="F31" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I31" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="10">
+        <v>9</v>
+      </c>
+      <c r="K31" t="s">
+        <v>48</v>
+      </c>
+      <c r="L31" s="10">
+        <v>48</v>
+      </c>
+      <c r="M31" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>32</v>
+      </c>
+      <c r="N31" t="s">
+        <v>63</v>
+      </c>
+      <c r="O31" t="s">
+        <v>33</v>
+      </c>
+      <c r="P31" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q31" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="R31" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="S31" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="T31" s="15">
+        <v>0</v>
+      </c>
+      <c r="U31" s="15">
+        <v>0</v>
+      </c>
+      <c r="V31" s="15">
+        <v>0</v>
+      </c>
+      <c r="W31" s="15">
+        <v>2</v>
+      </c>
+      <c r="X31" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="10">
         <v>8</v>
       </c>
-      <c r="K22" t="s">
+      <c r="Z31" s="10">
+        <v>5</v>
+      </c>
+      <c r="AA31" s="10">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>51</v>
+      </c>
+      <c r="B32" s="9">
+        <v>2</v>
+      </c>
+      <c r="C32" s="9">
+        <v>30</v>
+      </c>
+      <c r="D32" s="1">
+        <v>41517</v>
+      </c>
+      <c r="E32" s="10">
+        <v>16</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" t="s">
+        <v>46</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I32" t="s">
+        <v>116</v>
+      </c>
+      <c r="J32" s="10">
+        <v>22</v>
+      </c>
+      <c r="K32" t="s">
+        <v>117</v>
+      </c>
+      <c r="L32" s="10">
+        <v>18</v>
+      </c>
+      <c r="M32" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>2</v>
+      </c>
+      <c r="N32" t="s">
+        <v>49</v>
+      </c>
+      <c r="O32" t="s">
+        <v>33</v>
+      </c>
+      <c r="P32" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q32" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="R32" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="S32" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="T32" s="15">
+        <v>0</v>
+      </c>
+      <c r="U32" s="15">
+        <v>0</v>
+      </c>
+      <c r="V32" s="15">
+        <v>0</v>
+      </c>
+      <c r="W32" s="15">
+        <v>1</v>
+      </c>
+      <c r="X32" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="10">
+        <v>6</v>
+      </c>
+      <c r="Z32" s="10">
+        <v>11</v>
+      </c>
+      <c r="AA32" s="10">
+        <f t="shared" si="0"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>70</v>
+      </c>
+      <c r="B33" s="9">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9">
+        <v>31</v>
+      </c>
+      <c r="D33" s="1">
+        <v>46094</v>
+      </c>
+      <c r="E33" s="10">
+        <v>16</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="I33" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="10">
+        <v>6</v>
+      </c>
+      <c r="K33" t="s">
+        <v>48</v>
+      </c>
+      <c r="L33" s="10">
+        <v>19</v>
+      </c>
+      <c r="M33" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
+      </c>
+      <c r="N33" t="s">
+        <v>32</v>
+      </c>
+      <c r="O33" t="s">
+        <v>33</v>
+      </c>
+      <c r="P33" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="L22" s="10">
-        <v>21</v>
-      </c>
-      <c r="M22" t="s">
-        <v>51</v>
-      </c>
-      <c r="N22" t="s">
-        <v>62</v>
-      </c>
-      <c r="O22" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="P22" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="R22" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="S22" s="15">
-        <v>0</v>
-      </c>
-      <c r="T22" s="15">
-        <v>0</v>
-      </c>
-      <c r="U22" s="15">
-        <v>0</v>
-      </c>
-      <c r="V22" s="15">
-        <v>0</v>
-      </c>
-      <c r="W22" s="9">
-        <v>1</v>
-      </c>
-      <c r="X22" s="10">
-        <v>3</v>
-      </c>
-      <c r="Y22" s="9">
+      <c r="Q33" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="R33" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="S33" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="T33" s="15">
+        <v>0</v>
+      </c>
+      <c r="U33" s="15">
+        <v>1</v>
+      </c>
+      <c r="V33" s="15">
+        <v>0</v>
+      </c>
+      <c r="W33" s="15">
+        <v>2</v>
+      </c>
+      <c r="X33" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="10">
         <v>9</v>
       </c>
-      <c r="Z22" s="10">
-        <f t="shared" si="0"/>
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>41</v>
-      </c>
-      <c r="B23" s="9">
-        <v>0</v>
-      </c>
-      <c r="C23" s="9">
-        <v>21</v>
-      </c>
-      <c r="D23" s="1">
-        <v>29048</v>
-      </c>
-      <c r="E23" s="10">
-        <v>16</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G23" t="s">
-        <v>38</v>
-      </c>
-      <c r="H23" t="s">
-        <v>57</v>
-      </c>
-      <c r="I23" t="s">
-        <v>30</v>
-      </c>
-      <c r="J23" s="10">
-        <v>15</v>
-      </c>
-      <c r="K23" t="s">
-        <v>85</v>
-      </c>
-      <c r="L23" s="10">
-        <v>18</v>
-      </c>
-      <c r="M23" t="s">
-        <v>32</v>
-      </c>
-      <c r="N23" t="s">
-        <v>62</v>
-      </c>
-      <c r="O23" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="P23" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="R23" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="S23" s="15">
-        <v>0</v>
-      </c>
-      <c r="T23" s="15">
-        <v>1</v>
-      </c>
-      <c r="U23" s="15">
-        <v>0</v>
-      </c>
-      <c r="V23" s="15">
-        <v>0</v>
-      </c>
-      <c r="W23" s="9">
-        <v>1</v>
-      </c>
-      <c r="X23" s="10">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="10">
+      <c r="Z33" s="10">
         <v>7</v>
       </c>
-      <c r="Z23" s="10">
-        <f t="shared" si="0"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>63</v>
-      </c>
-      <c r="B24" s="9">
-        <v>0</v>
-      </c>
-      <c r="C24" s="9">
-        <v>22</v>
-      </c>
-      <c r="D24" s="1">
-        <v>29097</v>
-      </c>
-      <c r="E24" s="10">
-        <v>16</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" t="s">
-        <v>116</v>
-      </c>
-      <c r="I24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24" s="10">
-        <v>15</v>
-      </c>
-      <c r="K24" t="s">
-        <v>50</v>
-      </c>
-      <c r="L24" s="10">
-        <v>21</v>
-      </c>
-      <c r="M24" t="s">
-        <v>117</v>
-      </c>
-      <c r="N24" t="s">
-        <v>33</v>
-      </c>
-      <c r="O24" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="P24" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q24" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="R24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="S24" s="15">
-        <v>0</v>
-      </c>
-      <c r="T24" s="15">
-        <v>0</v>
-      </c>
-      <c r="U24" s="15">
-        <v>0</v>
-      </c>
-      <c r="V24" s="15">
-        <v>1</v>
-      </c>
-      <c r="W24" s="9">
-        <v>1</v>
-      </c>
-      <c r="X24" s="10">
-        <v>10</v>
-      </c>
-      <c r="Y24" s="10">
-        <v>8</v>
-      </c>
-      <c r="Z24" s="10">
+      <c r="AA33" s="10">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AA24" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>5</v>
-      </c>
-      <c r="B25" s="9">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9">
-        <v>23</v>
-      </c>
-      <c r="D25" s="1">
-        <v>34473</v>
-      </c>
-      <c r="E25" s="10">
-        <v>16</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25" t="s">
-        <v>67</v>
-      </c>
-      <c r="H25" t="s">
-        <v>39</v>
-      </c>
-      <c r="I25" t="s">
-        <v>84</v>
-      </c>
-      <c r="J25" s="10">
-        <v>30</v>
-      </c>
-      <c r="K25" t="s">
-        <v>31</v>
-      </c>
-      <c r="L25" s="10">
-        <v>19</v>
-      </c>
-      <c r="M25" t="s">
-        <v>32</v>
-      </c>
-      <c r="N25" t="s">
-        <v>33</v>
-      </c>
-      <c r="O25" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="P25" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q25" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="R25" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="S25" s="15">
-        <v>0</v>
-      </c>
-      <c r="T25" s="15">
-        <v>0</v>
-      </c>
-      <c r="U25" s="15">
-        <v>0</v>
-      </c>
-      <c r="V25" s="15">
-        <v>1</v>
-      </c>
-      <c r="W25" s="9">
-        <v>1</v>
-      </c>
-      <c r="X25" s="9">
-        <v>5</v>
-      </c>
-      <c r="Y25" s="9">
-        <v>6</v>
-      </c>
-      <c r="Z25" s="10">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>21</v>
-      </c>
-      <c r="B26" s="9">
-        <v>2</v>
-      </c>
-      <c r="C26" s="9">
-        <v>24</v>
-      </c>
-      <c r="D26" s="1">
-        <v>35217</v>
-      </c>
-      <c r="E26" s="10">
-        <v>16</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G26" t="s">
-        <v>121</v>
-      </c>
-      <c r="H26" t="s">
-        <v>48</v>
-      </c>
-      <c r="I26" t="s">
-        <v>79</v>
-      </c>
-      <c r="J26" s="10">
-        <v>60</v>
-      </c>
-      <c r="K26" t="s">
-        <v>75</v>
-      </c>
-      <c r="L26" s="10">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
-        <v>51</v>
-      </c>
-      <c r="N26" t="s">
-        <v>62</v>
-      </c>
-      <c r="O26" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="P26" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q26" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="R26" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="S26" s="15">
-        <v>0</v>
-      </c>
-      <c r="T26" s="15">
-        <v>0</v>
-      </c>
-      <c r="U26" s="15">
-        <v>0</v>
-      </c>
-      <c r="V26" s="15">
-        <v>0</v>
-      </c>
-      <c r="W26" s="9">
-        <v>1</v>
-      </c>
-      <c r="X26" s="10">
-        <v>4</v>
-      </c>
-      <c r="Y26" s="10">
-        <v>8</v>
-      </c>
-      <c r="Z26" s="10">
-        <f t="shared" si="0"/>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>16</v>
-      </c>
-      <c r="B27" s="9">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9">
-        <v>25</v>
-      </c>
-      <c r="D27" s="1">
-        <v>35745</v>
-      </c>
-      <c r="E27" s="10">
-        <v>16</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" t="s">
-        <v>74</v>
-      </c>
-      <c r="I27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J27" s="10">
-        <v>20</v>
-      </c>
-      <c r="K27" t="s">
-        <v>50</v>
-      </c>
-      <c r="L27" s="10">
-        <v>49</v>
-      </c>
-      <c r="M27" t="s">
-        <v>107</v>
-      </c>
-      <c r="N27" t="s">
-        <v>33</v>
-      </c>
-      <c r="O27" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="P27" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q27" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="R27" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="S27" s="15">
-        <v>0</v>
-      </c>
-      <c r="T27" s="15">
-        <v>1</v>
-      </c>
-      <c r="U27" s="15">
-        <v>0</v>
-      </c>
-      <c r="V27" s="14">
-        <v>-1</v>
-      </c>
-      <c r="W27" s="9">
-        <v>1</v>
-      </c>
-      <c r="X27" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="10">
-        <v>2</v>
-      </c>
-      <c r="Z27" s="10">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>7</v>
-      </c>
-      <c r="B28" s="9">
-        <v>2</v>
-      </c>
-      <c r="C28" s="9">
-        <v>26</v>
-      </c>
-      <c r="D28" s="1">
-        <v>37883</v>
-      </c>
-      <c r="E28" s="10">
-        <v>16</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" t="s">
-        <v>38</v>
-      </c>
-      <c r="H28" t="s">
-        <v>57</v>
-      </c>
-      <c r="I28" t="s">
-        <v>84</v>
-      </c>
-      <c r="J28" s="10">
-        <v>50</v>
-      </c>
-      <c r="K28" t="s">
-        <v>85</v>
-      </c>
-      <c r="L28" s="10">
-        <v>19</v>
-      </c>
-      <c r="M28" t="s">
-        <v>32</v>
-      </c>
-      <c r="N28" t="s">
-        <v>62</v>
-      </c>
-      <c r="O28" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q28" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="R28" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="S28" s="15">
-        <v>0</v>
-      </c>
-      <c r="T28" s="15">
-        <v>0</v>
-      </c>
-      <c r="U28" s="15">
-        <v>0</v>
-      </c>
-      <c r="V28" s="15">
-        <v>1</v>
-      </c>
-      <c r="W28" s="9">
-        <v>1</v>
-      </c>
-      <c r="X28" s="15">
-        <v>5</v>
-      </c>
-      <c r="Y28" s="9">
-        <v>9</v>
-      </c>
-      <c r="Z28" s="10">
-        <f t="shared" si="0"/>
-        <v>-4</v>
-      </c>
-      <c r="AA28" s="15"/>
-    </row>
-    <row r="29" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>73</v>
-      </c>
-      <c r="B29" s="9">
-        <v>3</v>
-      </c>
-      <c r="C29" s="9">
-        <v>27</v>
-      </c>
-      <c r="D29" s="1">
-        <v>38989</v>
-      </c>
-      <c r="E29" s="10">
-        <v>16</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" t="s">
-        <v>106</v>
-      </c>
-      <c r="I29" t="s">
-        <v>30</v>
-      </c>
-      <c r="J29" s="10">
-        <v>15</v>
-      </c>
-      <c r="K29" t="s">
-        <v>50</v>
-      </c>
-      <c r="L29" s="10">
-        <v>19</v>
-      </c>
-      <c r="M29" t="s">
-        <v>126</v>
-      </c>
-      <c r="N29" t="s">
-        <v>33</v>
-      </c>
-      <c r="O29" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="P29" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q29" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="R29" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="S29" s="14">
-        <v>-1</v>
-      </c>
-      <c r="T29" s="15">
-        <v>0</v>
-      </c>
-      <c r="U29" s="15">
-        <v>0</v>
-      </c>
-      <c r="V29" s="15">
-        <v>2</v>
-      </c>
-      <c r="W29" s="9">
-        <v>1</v>
-      </c>
-      <c r="X29" s="10">
-        <v>4</v>
-      </c>
-      <c r="Y29" s="10">
-        <v>7</v>
-      </c>
-      <c r="Z29" s="10">
-        <f t="shared" si="0"/>
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>60</v>
-      </c>
-      <c r="B30" s="9">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9">
-        <v>28</v>
-      </c>
-      <c r="D30" s="1">
-        <v>39692</v>
-      </c>
-      <c r="E30" s="10">
-        <v>23</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G30" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" t="s">
-        <v>39</v>
-      </c>
-      <c r="I30" t="s">
-        <v>40</v>
-      </c>
-      <c r="J30" s="10">
-        <v>5</v>
-      </c>
-      <c r="K30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L30" s="10">
-        <v>55</v>
-      </c>
-      <c r="M30" t="s">
-        <v>41</v>
-      </c>
-      <c r="N30" t="s">
-        <v>33</v>
-      </c>
-      <c r="O30" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="P30" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q30" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="R30" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="S30" s="15">
-        <v>0</v>
-      </c>
-      <c r="T30" s="15">
-        <v>1</v>
-      </c>
-      <c r="U30" s="15">
-        <v>0</v>
-      </c>
-      <c r="V30" s="15">
-        <v>0</v>
-      </c>
-      <c r="W30" s="9">
-        <v>1</v>
-      </c>
-      <c r="X30" s="10">
-        <v>12</v>
-      </c>
-      <c r="Y30" s="10">
-        <v>11</v>
-      </c>
-      <c r="Z30" s="10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>58</v>
-      </c>
-      <c r="B31" s="9">
-        <v>2</v>
-      </c>
-      <c r="C31" s="9">
-        <v>29</v>
-      </c>
-      <c r="D31" s="1">
-        <v>41473</v>
-      </c>
-      <c r="E31" s="10">
-        <v>16</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" t="s">
-        <v>38</v>
-      </c>
-      <c r="H31" t="s">
-        <v>39</v>
-      </c>
-      <c r="I31" t="s">
-        <v>30</v>
-      </c>
-      <c r="J31" s="10">
-        <v>9</v>
-      </c>
-      <c r="K31" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" s="10">
-        <v>48</v>
-      </c>
-      <c r="M31" t="s">
-        <v>68</v>
-      </c>
-      <c r="N31" t="s">
-        <v>33</v>
-      </c>
-      <c r="O31" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q31" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="R31" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="S31" s="15">
-        <v>0</v>
-      </c>
-      <c r="T31" s="15">
-        <v>0</v>
-      </c>
-      <c r="U31" s="15">
-        <v>0</v>
-      </c>
-      <c r="V31" s="15">
-        <v>2</v>
-      </c>
-      <c r="W31" s="9">
-        <v>1</v>
-      </c>
-      <c r="X31" s="10">
-        <v>8</v>
-      </c>
-      <c r="Y31" s="10">
-        <v>5</v>
-      </c>
-      <c r="Z31" s="10">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>51</v>
-      </c>
-      <c r="B32" s="9">
-        <v>2</v>
-      </c>
-      <c r="C32" s="9">
-        <v>30</v>
-      </c>
-      <c r="D32" s="1">
-        <v>41517</v>
-      </c>
-      <c r="E32" s="10">
-        <v>16</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G32" t="s">
-        <v>47</v>
-      </c>
-      <c r="H32" t="s">
-        <v>106</v>
-      </c>
-      <c r="I32" t="s">
-        <v>130</v>
-      </c>
-      <c r="J32" s="10">
-        <v>22</v>
-      </c>
-      <c r="K32" t="s">
-        <v>131</v>
-      </c>
-      <c r="L32" s="10">
-        <v>18</v>
-      </c>
-      <c r="M32" t="s">
-        <v>51</v>
-      </c>
-      <c r="N32" t="s">
-        <v>33</v>
-      </c>
-      <c r="O32" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="P32" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q32" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="R32" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="S32" s="15">
-        <v>0</v>
-      </c>
-      <c r="T32" s="15">
-        <v>0</v>
-      </c>
-      <c r="U32" s="15">
-        <v>0</v>
-      </c>
-      <c r="V32" s="15">
-        <v>1</v>
-      </c>
-      <c r="W32" s="9">
-        <v>1</v>
-      </c>
-      <c r="X32" s="10">
-        <v>6</v>
-      </c>
-      <c r="Y32" s="10">
-        <v>11</v>
-      </c>
-      <c r="Z32" s="10">
-        <f t="shared" si="0"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>70</v>
-      </c>
-      <c r="B33" s="9">
-        <v>0</v>
-      </c>
-      <c r="C33" s="9">
-        <v>31</v>
-      </c>
-      <c r="D33" s="1">
-        <v>46094</v>
-      </c>
-      <c r="E33" s="10">
-        <v>16</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G33" t="s">
-        <v>28</v>
-      </c>
-      <c r="H33" t="s">
-        <v>103</v>
-      </c>
-      <c r="I33" t="s">
-        <v>30</v>
-      </c>
-      <c r="J33" s="10">
-        <v>6</v>
-      </c>
-      <c r="K33" t="s">
-        <v>31</v>
-      </c>
-      <c r="L33" s="10">
-        <v>19</v>
-      </c>
-      <c r="M33" t="s">
-        <v>32</v>
-      </c>
-      <c r="N33" t="s">
-        <v>33</v>
-      </c>
-      <c r="O33" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="P33" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q33" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="R33" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S33" s="15">
-        <v>0</v>
-      </c>
-      <c r="T33" s="15">
-        <v>1</v>
-      </c>
-      <c r="U33" s="15">
-        <v>0</v>
-      </c>
-      <c r="V33" s="15">
-        <v>2</v>
-      </c>
-      <c r="W33" s="9">
-        <v>1</v>
-      </c>
-      <c r="X33" s="10">
-        <v>9</v>
-      </c>
-      <c r="Y33" s="10">
-        <v>7</v>
-      </c>
-      <c r="Z33" s="10">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>11</v>
       </c>
@@ -3826,46 +3952,47 @@
         <v>16</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H34" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I34" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="J34" s="10">
         <v>140</v>
       </c>
       <c r="K34" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="L34" s="10">
         <v>24</v>
       </c>
-      <c r="M34" t="s">
-        <v>107</v>
+      <c r="M34" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>8</v>
       </c>
       <c r="N34" t="s">
-        <v>62</v>
-      </c>
-      <c r="O34" s="13" t="s">
-        <v>81</v>
+        <v>95</v>
+      </c>
+      <c r="O34" t="s">
+        <v>57</v>
       </c>
       <c r="P34" s="13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Q34" s="13" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S34" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S34" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T34" s="15">
         <v>0</v>
@@ -3876,21 +4003,24 @@
       <c r="V34" s="15">
         <v>0</v>
       </c>
-      <c r="W34" s="9">
-        <v>1</v>
-      </c>
-      <c r="X34" s="10">
+      <c r="W34" s="15">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="10">
         <v>4</v>
       </c>
-      <c r="Y34" s="9">
+      <c r="Z34" s="9">
         <v>14</v>
       </c>
-      <c r="Z34" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA34" s="10">
+        <f t="shared" ref="AA34:AA65" si="1">Y34-Z34</f>
         <v>-10</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>42</v>
       </c>
@@ -3907,74 +4037,78 @@
         <v>16</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G35" t="s">
         <v>38</v>
       </c>
-      <c r="H35" t="s">
-        <v>57</v>
+      <c r="H35" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J35" s="10">
         <v>10</v>
       </c>
       <c r="K35" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="L35" s="10">
         <v>18</v>
       </c>
-      <c r="M35" t="s">
+      <c r="M35" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>2</v>
+      </c>
+      <c r="N35" t="s">
         <v>32</v>
       </c>
-      <c r="N35" t="s">
-        <v>62</v>
-      </c>
-      <c r="O35" s="13" t="s">
-        <v>69</v>
+      <c r="O35" t="s">
+        <v>57</v>
       </c>
       <c r="P35" s="13" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="Q35" s="13" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="R35" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="S35" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S35" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="T35" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="15">
+        <v>0</v>
+      </c>
+      <c r="W35" s="15">
         <v>2</v>
       </c>
-      <c r="W35" s="9">
-        <v>1</v>
-      </c>
-      <c r="X35" s="10">
-        <v>0</v>
+      <c r="X35" s="9">
+        <v>1</v>
       </c>
       <c r="Y35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="10">
         <v>13</v>
       </c>
-      <c r="Z35" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA35" s="10">
+        <f t="shared" si="1"/>
         <v>-13</v>
       </c>
-      <c r="AA35" s="13" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB35" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>6</v>
       </c>
@@ -3991,71 +4125,75 @@
         <v>16</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G36" t="s">
         <v>38</v>
       </c>
-      <c r="H36" t="s">
-        <v>39</v>
+      <c r="H36" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J36" s="10">
         <v>100</v>
       </c>
       <c r="K36" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="L36" s="10">
         <v>19</v>
       </c>
-      <c r="M36" t="s">
+      <c r="M36" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
+      </c>
+      <c r="N36" t="s">
         <v>32</v>
       </c>
-      <c r="N36" t="s">
-        <v>62</v>
-      </c>
-      <c r="O36" s="13" t="s">
-        <v>44</v>
+      <c r="O36" t="s">
+        <v>57</v>
       </c>
       <c r="P36" s="13" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="Q36" s="13" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="R36" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S36" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S36" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T36" s="15">
+        <v>0</v>
+      </c>
+      <c r="U36" s="15">
         <v>2</v>
       </c>
-      <c r="U36" s="15">
-        <v>0</v>
-      </c>
       <c r="V36" s="15">
         <v>0</v>
       </c>
-      <c r="W36" s="9">
-        <v>1</v>
+      <c r="W36" s="15">
+        <v>0</v>
       </c>
       <c r="X36" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="9">
         <v>5</v>
       </c>
-      <c r="Y36" s="9">
+      <c r="Z36" s="9">
         <v>8</v>
       </c>
-      <c r="Z36" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA36" s="10">
+        <f t="shared" si="1"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>9</v>
       </c>
@@ -4072,72 +4210,76 @@
         <v>17</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G37" t="s">
-        <v>73</v>
-      </c>
-      <c r="H37" t="s">
-        <v>114</v>
+        <v>67</v>
+      </c>
+      <c r="H37" s="24" t="s">
+        <v>177</v>
       </c>
       <c r="I37" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J37" s="10">
         <v>10</v>
       </c>
       <c r="K37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L37" s="10">
         <v>25</v>
       </c>
-      <c r="M37" t="s">
-        <v>107</v>
+      <c r="M37" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>8</v>
       </c>
       <c r="N37" t="s">
+        <v>95</v>
+      </c>
+      <c r="O37" t="s">
         <v>33</v>
       </c>
-      <c r="O37" s="13" t="s">
-        <v>139</v>
-      </c>
       <c r="P37" s="13" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="Q37" s="13" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="R37" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S37" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S37" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T37" s="15">
+        <v>0</v>
+      </c>
+      <c r="U37" s="15">
         <v>2</v>
       </c>
-      <c r="U37" s="15">
-        <v>0</v>
-      </c>
       <c r="V37" s="15">
         <v>0</v>
       </c>
-      <c r="W37" s="9">
-        <v>1</v>
-      </c>
-      <c r="X37" s="15">
+      <c r="W37" s="15">
+        <v>0</v>
+      </c>
+      <c r="X37" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="15">
         <v>20</v>
       </c>
-      <c r="Y37" s="9">
+      <c r="Z37" s="9">
         <v>26</v>
       </c>
-      <c r="Z37" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA37" s="10">
+        <f t="shared" si="1"/>
         <v>-6</v>
       </c>
-      <c r="AA37" s="15"/>
-    </row>
-    <row r="38" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB37" s="15"/>
+    </row>
+    <row r="38" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>22</v>
       </c>
@@ -4154,74 +4296,78 @@
         <v>16</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H38" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J38" s="10">
         <v>5</v>
       </c>
       <c r="K38" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L38" s="10">
         <v>20</v>
       </c>
-      <c r="M38" t="s">
-        <v>51</v>
+      <c r="M38" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>4</v>
       </c>
       <c r="N38" t="s">
+        <v>49</v>
+      </c>
+      <c r="O38" t="s">
         <v>33</v>
       </c>
-      <c r="O38" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="P38" s="13" t="s">
-        <v>142</v>
+      <c r="P38" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="Q38" s="13" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="R38" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S38" s="14">
+        <v>129</v>
+      </c>
+      <c r="S38" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="T38" s="14">
         <v>-1</v>
       </c>
-      <c r="T38" s="15">
-        <v>0</v>
-      </c>
       <c r="U38" s="15">
         <v>0</v>
       </c>
       <c r="V38" s="15">
         <v>0</v>
       </c>
-      <c r="W38" s="9">
-        <v>1</v>
-      </c>
-      <c r="X38" s="10">
+      <c r="W38" s="15">
+        <v>0</v>
+      </c>
+      <c r="X38" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="10">
         <v>7</v>
       </c>
-      <c r="Y38" s="10">
+      <c r="Z38" s="10">
         <v>11</v>
       </c>
-      <c r="Z38" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA38" s="10">
+        <f t="shared" si="1"/>
         <v>-4</v>
       </c>
-      <c r="AA38" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB38" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>57</v>
       </c>
@@ -4238,46 +4384,47 @@
         <v>16</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G39" t="s">
         <v>38</v>
       </c>
-      <c r="H39" t="s">
-        <v>57</v>
+      <c r="H39" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J39" s="10">
         <v>12</v>
       </c>
       <c r="K39" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L39" s="10">
         <v>51</v>
       </c>
-      <c r="M39" t="s">
-        <v>41</v>
+      <c r="M39" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>35</v>
       </c>
       <c r="N39" t="s">
-        <v>62</v>
-      </c>
-      <c r="O39" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O39" t="s">
+        <v>57</v>
+      </c>
+      <c r="P39" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="P39" s="13" t="s">
-        <v>43</v>
-      </c>
       <c r="Q39" s="13" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="R39" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="S39" s="15">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="S39" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="T39" s="15">
         <v>0</v>
@@ -4288,24 +4435,27 @@
       <c r="V39" s="15">
         <v>0</v>
       </c>
-      <c r="W39" s="9">
-        <v>1</v>
-      </c>
-      <c r="X39" s="10">
+      <c r="W39" s="15">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y39" s="10">
         <v>7</v>
       </c>
-      <c r="Y39" s="10">
+      <c r="Z39" s="10">
         <v>5</v>
       </c>
-      <c r="Z39" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA39" s="10">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="AA39" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB39" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>43</v>
       </c>
@@ -4322,74 +4472,78 @@
         <v>16</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G40" t="s">
         <v>38</v>
       </c>
-      <c r="H40" t="s">
-        <v>57</v>
+      <c r="H40" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J40" s="10">
         <v>20</v>
       </c>
       <c r="K40" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L40" s="10">
         <v>20</v>
       </c>
-      <c r="M40" t="s">
+      <c r="M40" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>4</v>
+      </c>
+      <c r="N40" t="s">
         <v>32</v>
       </c>
-      <c r="N40" t="s">
-        <v>62</v>
-      </c>
-      <c r="O40" s="12" t="s">
+      <c r="O40" t="s">
+        <v>57</v>
+      </c>
+      <c r="P40" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="P40" s="13" t="s">
-        <v>43</v>
-      </c>
       <c r="Q40" s="13" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="R40" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="S40" s="14">
+        <v>66</v>
+      </c>
+      <c r="S40" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="T40" s="14">
         <v>-1</v>
       </c>
-      <c r="T40" s="15">
-        <v>0</v>
-      </c>
       <c r="U40" s="15">
         <v>0</v>
       </c>
       <c r="V40" s="15">
+        <v>0</v>
+      </c>
+      <c r="W40" s="15">
         <v>2</v>
       </c>
-      <c r="W40" s="9">
-        <v>1</v>
-      </c>
-      <c r="X40" s="10">
+      <c r="X40" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="10">
         <v>5</v>
       </c>
-      <c r="Y40" s="10">
+      <c r="Z40" s="10">
         <v>6</v>
       </c>
-      <c r="Z40" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA40" s="10">
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="AA40" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB40" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -4406,71 +4560,75 @@
         <v>16</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G41" t="s">
-        <v>73</v>
-      </c>
-      <c r="H41" t="s">
-        <v>106</v>
+        <v>67</v>
+      </c>
+      <c r="H41" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I41" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J41" s="10">
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L41" s="10">
         <v>26</v>
       </c>
-      <c r="M41" t="s">
-        <v>149</v>
+      <c r="M41" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>10</v>
       </c>
       <c r="N41" t="s">
-        <v>62</v>
-      </c>
-      <c r="O41" s="13" t="s">
-        <v>150</v>
+        <v>135</v>
+      </c>
+      <c r="O41" t="s">
+        <v>57</v>
       </c>
       <c r="P41" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q41" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="R41" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S41" s="15">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="Q41" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="R41" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="S41" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T41" s="15">
-        <v>1</v>
-      </c>
-      <c r="U41" s="14">
+        <v>0</v>
+      </c>
+      <c r="U41" s="15">
+        <v>1</v>
+      </c>
+      <c r="V41" s="14">
         <v>-1</v>
       </c>
-      <c r="V41" s="15">
-        <v>0</v>
-      </c>
-      <c r="W41" s="9">
-        <v>1</v>
+      <c r="W41" s="15">
+        <v>0</v>
       </c>
       <c r="X41" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="9">
         <v>7</v>
       </c>
-      <c r="Y41" s="9">
+      <c r="Z41" s="9">
         <v>10</v>
       </c>
-      <c r="Z41" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA41" s="10">
+        <f t="shared" si="1"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>14</v>
       </c>
@@ -4487,71 +4645,75 @@
         <v>16</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G42" t="s">
-        <v>153</v>
-      </c>
-      <c r="H42" t="s">
-        <v>48</v>
+        <v>139</v>
+      </c>
+      <c r="H42" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I42" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="J42" s="10">
         <v>30</v>
       </c>
       <c r="K42" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="L42" s="10">
         <v>20</v>
       </c>
-      <c r="M42" t="s">
-        <v>51</v>
+      <c r="M42" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>4</v>
       </c>
       <c r="N42" t="s">
+        <v>49</v>
+      </c>
+      <c r="O42" t="s">
         <v>33</v>
       </c>
-      <c r="O42" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="P42" s="13" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="Q42" s="13" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="R42" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S42" s="15">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="S42" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T42" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U42" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="15">
         <v>0</v>
       </c>
-      <c r="W42" s="9">
-        <v>1</v>
-      </c>
-      <c r="X42" s="10">
+      <c r="W42" s="15">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y42" s="10">
         <v>3</v>
       </c>
-      <c r="Y42" s="9">
+      <c r="Z42" s="9">
         <v>7</v>
       </c>
-      <c r="Z42" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA42" s="10">
+        <f t="shared" si="1"/>
         <v>-4</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -4568,74 +4730,78 @@
         <v>17</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G43" t="s">
         <v>38</v>
       </c>
-      <c r="H43" t="s">
-        <v>39</v>
+      <c r="H43" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J43" s="10">
         <v>10</v>
       </c>
       <c r="K43" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L43" s="10">
         <v>21</v>
       </c>
-      <c r="M43" t="s">
-        <v>68</v>
+      <c r="M43" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>4</v>
       </c>
       <c r="N43" t="s">
-        <v>62</v>
-      </c>
-      <c r="O43" s="13" t="s">
-        <v>42</v>
+        <v>63</v>
+      </c>
+      <c r="O43" t="s">
+        <v>57</v>
       </c>
       <c r="P43" s="13" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="Q43" s="13" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="R43" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S43" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S43" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T43" s="15">
+        <v>0</v>
+      </c>
+      <c r="U43" s="15">
         <v>2</v>
       </c>
-      <c r="U43" s="15">
-        <v>0</v>
-      </c>
       <c r="V43" s="15">
         <v>0</v>
       </c>
-      <c r="W43" s="9">
-        <v>1</v>
-      </c>
-      <c r="X43" s="10">
+      <c r="W43" s="15">
+        <v>0</v>
+      </c>
+      <c r="X43" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="10">
         <v>7</v>
       </c>
-      <c r="Y43" s="10">
+      <c r="Z43" s="10">
         <v>4</v>
       </c>
-      <c r="Z43" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA43" s="10">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="AA43" s="13" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB43" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>68</v>
       </c>
@@ -4652,46 +4818,47 @@
         <v>16</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G44" t="s">
         <v>38</v>
       </c>
-      <c r="H44" t="s">
-        <v>29</v>
+      <c r="H44" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J44" s="10">
         <v>20</v>
       </c>
       <c r="K44" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="L44" s="10">
         <v>28</v>
       </c>
-      <c r="M44" t="s">
-        <v>68</v>
+      <c r="M44" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>12</v>
       </c>
       <c r="N44" t="s">
-        <v>62</v>
-      </c>
-      <c r="O44" s="13" t="s">
-        <v>129</v>
+        <v>63</v>
+      </c>
+      <c r="O44" t="s">
+        <v>57</v>
       </c>
       <c r="P44" s="13" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="Q44" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="R44" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="R44" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="S44" s="15">
-        <v>0</v>
+      <c r="S44" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="T44" s="15">
         <v>0</v>
@@ -4702,21 +4869,24 @@
       <c r="V44" s="15">
         <v>0</v>
       </c>
-      <c r="W44" s="9">
-        <v>1</v>
-      </c>
-      <c r="X44" s="10">
-        <v>9</v>
+      <c r="W44" s="15">
+        <v>0</v>
+      </c>
+      <c r="X44" s="9">
+        <v>1</v>
       </c>
       <c r="Y44" s="10">
         <v>9</v>
       </c>
       <c r="Z44" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="AA44" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>15</v>
       </c>
@@ -4733,46 +4903,47 @@
         <v>16</v>
       </c>
       <c r="F45" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="I45" t="s">
         <v>72</v>
-      </c>
-      <c r="G45" t="s">
-        <v>73</v>
-      </c>
-      <c r="H45" t="s">
-        <v>74</v>
-      </c>
-      <c r="I45" t="s">
-        <v>79</v>
       </c>
       <c r="J45" s="10">
         <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L45" s="10">
         <v>24</v>
       </c>
-      <c r="M45" t="s">
-        <v>76</v>
+      <c r="M45" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>8</v>
       </c>
       <c r="N45" t="s">
-        <v>62</v>
-      </c>
-      <c r="O45" s="13" t="s">
-        <v>44</v>
+        <v>69</v>
+      </c>
+      <c r="O45" t="s">
+        <v>57</v>
       </c>
       <c r="P45" s="13" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="Q45" s="13" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="R45" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S45" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S45" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T45" s="15">
         <v>0</v>
@@ -4783,21 +4954,24 @@
       <c r="V45" s="15">
         <v>0</v>
       </c>
-      <c r="W45" s="9">
-        <v>1</v>
-      </c>
-      <c r="X45" s="10">
+      <c r="W45" s="15">
+        <v>0</v>
+      </c>
+      <c r="X45" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y45" s="10">
         <v>5</v>
       </c>
-      <c r="Y45" s="9">
+      <c r="Z45" s="9">
         <v>14</v>
       </c>
-      <c r="Z45" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA45" s="10">
+        <f t="shared" si="1"/>
         <v>-9</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>25</v>
       </c>
@@ -4814,71 +4988,75 @@
         <v>16</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G46" t="s">
         <v>38</v>
       </c>
-      <c r="H46" t="s">
-        <v>57</v>
+      <c r="H46" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J46" s="10">
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L46" s="10">
         <v>19</v>
       </c>
-      <c r="M46" t="s">
+      <c r="M46" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
+      </c>
+      <c r="N46" t="s">
         <v>32</v>
       </c>
-      <c r="N46" t="s">
+      <c r="O46" t="s">
         <v>33</v>
       </c>
-      <c r="O46" s="12" t="s">
-        <v>141</v>
-      </c>
       <c r="P46" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q46" s="13" t="s">
-        <v>44</v>
+        <v>127</v>
+      </c>
+      <c r="Q46" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="R46" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="S46" s="14">
-        <v>-1</v>
+        <v>43</v>
+      </c>
+      <c r="S46" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="T46" s="14">
         <v>-1</v>
       </c>
-      <c r="U46" s="15">
-        <v>0</v>
+      <c r="U46" s="14">
+        <v>-1</v>
       </c>
       <c r="V46" s="15">
+        <v>0</v>
+      </c>
+      <c r="W46" s="15">
         <v>2</v>
       </c>
-      <c r="W46" s="9">
-        <v>1</v>
-      </c>
-      <c r="X46" s="10">
+      <c r="X46" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y46" s="10">
         <v>5</v>
       </c>
-      <c r="Y46" s="10">
+      <c r="Z46" s="10">
         <v>9</v>
       </c>
-      <c r="Z46" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA46" s="10">
+        <f t="shared" si="1"/>
         <v>-4</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>19</v>
       </c>
@@ -4895,46 +5073,47 @@
         <v>16</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G47" t="s">
-        <v>73</v>
-      </c>
-      <c r="H47" t="s">
-        <v>106</v>
+        <v>67</v>
+      </c>
+      <c r="H47" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I47" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J47" s="10">
         <v>11</v>
       </c>
       <c r="K47" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="L47" s="10">
         <v>22</v>
       </c>
-      <c r="M47" t="s">
-        <v>51</v>
+      <c r="M47" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>6</v>
       </c>
       <c r="N47" t="s">
-        <v>62</v>
-      </c>
-      <c r="O47" s="13" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="O47" t="s">
+        <v>57</v>
       </c>
       <c r="P47" s="13" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="Q47" s="13" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="R47" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S47" s="15">
-        <v>0</v>
+        <v>145</v>
+      </c>
+      <c r="S47" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T47" s="15">
         <v>0</v>
@@ -4945,21 +5124,24 @@
       <c r="V47" s="15">
         <v>0</v>
       </c>
-      <c r="W47" s="9">
-        <v>1</v>
-      </c>
-      <c r="X47" s="10">
+      <c r="W47" s="15">
+        <v>0</v>
+      </c>
+      <c r="X47" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y47" s="10">
         <v>8</v>
       </c>
-      <c r="Y47" s="10">
+      <c r="Z47" s="10">
         <v>11</v>
       </c>
-      <c r="Z47" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA47" s="10">
+        <f t="shared" si="1"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>29</v>
       </c>
@@ -4976,46 +5158,47 @@
         <v>16</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G48" t="s">
         <v>38</v>
       </c>
-      <c r="H48" t="s">
-        <v>29</v>
+      <c r="H48" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J48" s="10">
         <v>10</v>
       </c>
       <c r="K48" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L48" s="10">
         <v>26</v>
       </c>
-      <c r="M48" t="s">
-        <v>41</v>
+      <c r="M48" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>10</v>
       </c>
       <c r="N48" t="s">
+        <v>40</v>
+      </c>
+      <c r="O48" t="s">
         <v>33</v>
-      </c>
-      <c r="O48" s="13" t="s">
-        <v>44</v>
       </c>
       <c r="P48" s="13" t="s">
         <v>43</v>
       </c>
       <c r="Q48" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="R48" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S48" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S48" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T48" s="15">
         <v>0</v>
@@ -5026,21 +5209,24 @@
       <c r="V48" s="15">
         <v>0</v>
       </c>
-      <c r="W48" s="9">
-        <v>1</v>
-      </c>
-      <c r="X48" s="10">
-        <v>6</v>
+      <c r="W48" s="15">
+        <v>0</v>
+      </c>
+      <c r="X48" s="9">
+        <v>1</v>
       </c>
       <c r="Y48" s="10">
         <v>6</v>
       </c>
       <c r="Z48" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="AA48" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>33</v>
       </c>
@@ -5057,46 +5243,47 @@
         <v>16</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G49" t="s">
         <v>38</v>
       </c>
-      <c r="H49" t="s">
-        <v>57</v>
+      <c r="H49" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I49" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="J49" s="10">
         <v>80</v>
       </c>
       <c r="K49" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="L49" s="10">
         <v>23</v>
       </c>
-      <c r="M49" t="s">
-        <v>107</v>
+      <c r="M49" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>7</v>
       </c>
       <c r="N49" t="s">
-        <v>62</v>
-      </c>
-      <c r="O49" s="13" t="s">
-        <v>44</v>
+        <v>95</v>
+      </c>
+      <c r="O49" t="s">
+        <v>57</v>
       </c>
       <c r="P49" s="13" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="Q49" s="13" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="R49" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S49" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S49" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T49" s="15">
         <v>0</v>
@@ -5107,24 +5294,27 @@
       <c r="V49" s="15">
         <v>0</v>
       </c>
-      <c r="W49" s="9">
-        <v>1</v>
-      </c>
-      <c r="X49" s="10">
+      <c r="W49" s="15">
+        <v>0</v>
+      </c>
+      <c r="X49" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y49" s="10">
         <v>7</v>
       </c>
-      <c r="Y49" s="10">
+      <c r="Z49" s="10">
         <v>11</v>
       </c>
-      <c r="Z49" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA49" s="10">
+        <f t="shared" si="1"/>
         <v>-4</v>
       </c>
-      <c r="AA49" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="50" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB49" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>37</v>
       </c>
@@ -5141,46 +5331,47 @@
         <v>16</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G50" t="s">
         <v>38</v>
       </c>
-      <c r="H50" t="s">
-        <v>39</v>
+      <c r="H50" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I50" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J50" s="10">
         <v>20</v>
       </c>
       <c r="K50" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L50" s="10">
         <v>26</v>
       </c>
-      <c r="M50" t="s">
-        <v>41</v>
+      <c r="M50" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>10</v>
       </c>
       <c r="N50" t="s">
-        <v>62</v>
-      </c>
-      <c r="O50" s="13" t="s">
-        <v>81</v>
+        <v>40</v>
+      </c>
+      <c r="O50" t="s">
+        <v>57</v>
       </c>
       <c r="P50" s="13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Q50" s="13" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="R50" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S50" s="15">
-        <v>0</v>
+        <v>146</v>
+      </c>
+      <c r="S50" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T50" s="15">
         <v>0</v>
@@ -5191,21 +5382,24 @@
       <c r="V50" s="15">
         <v>0</v>
       </c>
-      <c r="W50" s="9">
-        <v>1</v>
-      </c>
-      <c r="X50" s="10">
+      <c r="W50" s="15">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="10">
         <v>4</v>
       </c>
-      <c r="Y50" s="10">
+      <c r="Z50" s="10">
         <v>9</v>
       </c>
-      <c r="Z50" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA50" s="10">
+        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>3</v>
       </c>
@@ -5222,74 +5416,78 @@
         <v>18</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G51" t="s">
-        <v>161</v>
-      </c>
-      <c r="H51" t="s">
-        <v>29</v>
+        <v>147</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J51" s="10">
         <v>5</v>
       </c>
       <c r="K51" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L51" s="10">
         <v>21</v>
       </c>
-      <c r="M51" t="s">
+      <c r="M51" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
+      </c>
+      <c r="N51" t="s">
         <v>32</v>
       </c>
-      <c r="N51" t="s">
+      <c r="O51" t="s">
         <v>33</v>
       </c>
-      <c r="O51" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="P51" s="13" t="s">
-        <v>78</v>
+      <c r="P51" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="Q51" s="13" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="R51" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="S51" s="14">
+        <v>74</v>
+      </c>
+      <c r="S51" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="T51" s="14">
         <v>-1</v>
       </c>
-      <c r="T51" s="15">
-        <v>0</v>
-      </c>
       <c r="U51" s="15">
         <v>0</v>
       </c>
       <c r="V51" s="15">
-        <v>1</v>
-      </c>
-      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="15">
         <v>1</v>
       </c>
       <c r="X51" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="9">
         <v>2</v>
       </c>
-      <c r="Y51" s="9">
+      <c r="Z51" s="9">
         <v>15</v>
       </c>
-      <c r="Z51" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA51" s="10">
+        <f t="shared" si="1"/>
         <v>-13</v>
       </c>
-      <c r="AA51" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="52" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB51" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>61</v>
       </c>
@@ -5306,46 +5504,47 @@
         <v>17</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G52" t="s">
         <v>38</v>
       </c>
-      <c r="H52" t="s">
-        <v>39</v>
+      <c r="H52" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J52" s="10">
         <v>8</v>
       </c>
       <c r="K52" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L52" s="10">
         <v>24</v>
       </c>
-      <c r="M52" t="s">
-        <v>41</v>
+      <c r="M52" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>7</v>
       </c>
       <c r="N52" t="s">
+        <v>40</v>
+      </c>
+      <c r="O52" t="s">
         <v>33</v>
       </c>
-      <c r="O52" s="13" t="s">
-        <v>165</v>
-      </c>
       <c r="P52" s="13" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="Q52" s="13" t="s">
-        <v>44</v>
+        <v>152</v>
       </c>
       <c r="R52" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="S52" s="15">
-        <v>0</v>
+      <c r="S52" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="T52" s="15">
         <v>0</v>
@@ -5356,23 +5555,26 @@
       <c r="V52" s="15">
         <v>0</v>
       </c>
-      <c r="W52" s="9">
-        <v>1</v>
-      </c>
-      <c r="X52" s="10">
+      <c r="W52" s="15">
+        <v>0</v>
+      </c>
+      <c r="X52" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="10">
         <v>4</v>
       </c>
-      <c r="Y52" s="10">
+      <c r="Z52" s="10">
         <v>7</v>
       </c>
-      <c r="Z52" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA52" s="10">
+        <f t="shared" si="1"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B53" s="9">
         <v>0</v>
@@ -5381,52 +5583,53 @@
         <v>51</v>
       </c>
       <c r="D53" s="1">
-        <v>64765</v>
+        <v>97973</v>
       </c>
       <c r="E53" s="10">
         <v>16</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G53" t="s">
-        <v>38</v>
-      </c>
-      <c r="H53" t="s">
-        <v>39</v>
+        <v>139</v>
+      </c>
+      <c r="H53" s="24" t="s">
+        <v>177</v>
       </c>
       <c r="I53" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="J53" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L53" s="10">
-        <v>26</v>
-      </c>
-      <c r="M53" t="s">
-        <v>167</v>
+        <v>21</v>
+      </c>
+      <c r="M53" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>5</v>
       </c>
       <c r="N53" t="s">
+        <v>49</v>
+      </c>
+      <c r="O53" t="s">
         <v>33</v>
-      </c>
-      <c r="O53" s="13" t="s">
-        <v>63</v>
       </c>
       <c r="P53" s="13" t="s">
         <v>43</v>
       </c>
       <c r="Q53" s="13" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="R53" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="S53" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S53" s="13" t="s">
+        <v>172</v>
       </c>
       <c r="T53" s="15">
         <v>0</v>
@@ -5437,21 +5640,24 @@
       <c r="V53" s="15">
         <v>0</v>
       </c>
-      <c r="W53" s="9">
-        <v>1</v>
-      </c>
-      <c r="X53" s="10">
-        <v>6</v>
+      <c r="W53" s="15">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>1</v>
       </c>
       <c r="Y53" s="10">
-        <v>13</v>
-      </c>
-      <c r="Z53" s="10">
-        <f t="shared" si="0"/>
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>10</v>
+      </c>
+      <c r="AA53" s="10">
+        <f>Y53-Z53</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -5468,46 +5674,47 @@
         <v>16</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G54" t="s">
-        <v>73</v>
-      </c>
-      <c r="H54" t="s">
-        <v>106</v>
+        <v>67</v>
+      </c>
+      <c r="H54" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J54" s="10">
         <v>20</v>
       </c>
       <c r="K54" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L54" s="10">
         <v>19</v>
       </c>
-      <c r="M54" t="s">
-        <v>51</v>
+      <c r="M54" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
       </c>
       <c r="N54" t="s">
-        <v>62</v>
-      </c>
-      <c r="O54" s="13" t="s">
-        <v>69</v>
+        <v>49</v>
+      </c>
+      <c r="O54" t="s">
+        <v>57</v>
       </c>
       <c r="P54" s="13" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="Q54" s="13" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="R54" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="S54" s="15">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="S54" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="T54" s="15">
         <v>0</v>
@@ -5518,21 +5725,24 @@
       <c r="V54" s="15">
         <v>0</v>
       </c>
-      <c r="W54" s="9">
-        <v>1</v>
-      </c>
-      <c r="X54" s="10">
+      <c r="W54" s="15">
+        <v>0</v>
+      </c>
+      <c r="X54" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y54" s="10">
         <v>7</v>
       </c>
-      <c r="Y54" s="10">
+      <c r="Z54" s="10">
         <v>8</v>
       </c>
-      <c r="Z54" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA54" s="10">
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46</v>
       </c>
@@ -5549,46 +5759,47 @@
         <v>16</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G55" t="s">
-        <v>28</v>
-      </c>
-      <c r="H55" t="s">
-        <v>103</v>
+        <v>30</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>177</v>
       </c>
       <c r="I55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J55" s="10">
         <v>10</v>
       </c>
       <c r="K55" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L55" s="10">
         <v>21</v>
       </c>
-      <c r="M55" t="s">
+      <c r="M55" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>5</v>
+      </c>
+      <c r="N55" t="s">
         <v>32</v>
       </c>
-      <c r="N55" t="s">
+      <c r="O55" t="s">
         <v>33</v>
       </c>
-      <c r="O55" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="P55" s="13" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="Q55" s="13" t="s">
-        <v>168</v>
+        <v>65</v>
       </c>
       <c r="R55" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="S55" s="15">
-        <v>0</v>
+        <v>154</v>
+      </c>
+      <c r="S55" s="13" t="s">
+        <v>155</v>
       </c>
       <c r="T55" s="15">
         <v>0</v>
@@ -5597,23 +5808,26 @@
         <v>0</v>
       </c>
       <c r="V55" s="15">
-        <v>1</v>
-      </c>
-      <c r="W55" s="9">
-        <v>1</v>
-      </c>
-      <c r="X55" s="10">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="W55" s="15">
+        <v>1</v>
+      </c>
+      <c r="X55" s="9">
+        <v>1</v>
       </c>
       <c r="Y55" s="10">
         <v>4</v>
       </c>
       <c r="Z55" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="AA55" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>45</v>
       </c>
@@ -5630,71 +5844,75 @@
         <v>16</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G56" t="s">
-        <v>28</v>
-      </c>
-      <c r="H56" t="s">
-        <v>103</v>
+        <v>30</v>
+      </c>
+      <c r="H56" s="24" t="s">
+        <v>177</v>
       </c>
       <c r="I56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J56" s="10">
         <v>7</v>
       </c>
       <c r="K56" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L56" s="10">
         <v>21</v>
       </c>
-      <c r="M56" t="s">
+      <c r="M56" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>5</v>
+      </c>
+      <c r="N56" t="s">
         <v>32</v>
       </c>
-      <c r="N56" t="s">
-        <v>170</v>
-      </c>
-      <c r="O56" s="13" t="s">
-        <v>69</v>
+      <c r="O56" t="s">
+        <v>33</v>
       </c>
       <c r="P56" s="13" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="Q56" s="13" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="R56" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S56" s="15">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="S56" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T56" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U56" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="15">
         <v>0</v>
       </c>
-      <c r="W56" s="9">
-        <v>1</v>
-      </c>
-      <c r="X56" s="10">
-        <v>5</v>
+      <c r="W56" s="15">
+        <v>0</v>
+      </c>
+      <c r="X56" s="9">
+        <v>1</v>
       </c>
       <c r="Y56" s="10">
         <v>5</v>
       </c>
       <c r="Z56" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="AA56" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>50</v>
       </c>
@@ -5711,71 +5929,75 @@
         <v>16</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G57" t="s">
-        <v>73</v>
-      </c>
-      <c r="H57" t="s">
-        <v>48</v>
+        <v>67</v>
+      </c>
+      <c r="H57" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I57" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="J57" s="10">
         <v>150</v>
       </c>
       <c r="K57" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="L57" s="10">
         <v>18</v>
       </c>
-      <c r="M57" t="s">
-        <v>51</v>
+      <c r="M57" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>2</v>
       </c>
       <c r="N57" t="s">
-        <v>62</v>
-      </c>
-      <c r="O57" s="13" t="s">
-        <v>63</v>
+        <v>49</v>
+      </c>
+      <c r="O57" t="s">
+        <v>57</v>
       </c>
       <c r="P57" s="13" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="Q57" s="13" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="R57" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="S57" s="15">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="S57" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="T57" s="15">
+        <v>0</v>
+      </c>
+      <c r="U57" s="15">
         <v>2</v>
       </c>
-      <c r="U57" s="15">
-        <v>0</v>
-      </c>
       <c r="V57" s="15">
         <v>0</v>
       </c>
-      <c r="W57" s="9">
-        <v>1</v>
-      </c>
-      <c r="X57" s="10">
+      <c r="W57" s="15">
+        <v>0</v>
+      </c>
+      <c r="X57" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y57" s="10">
         <v>8</v>
       </c>
-      <c r="Y57" s="10">
+      <c r="Z57" s="10">
         <v>10</v>
       </c>
-      <c r="Z57" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA57" s="10">
+        <f t="shared" si="1"/>
         <v>-2</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>67</v>
       </c>
@@ -5792,46 +6014,47 @@
         <v>16</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G58" t="s">
         <v>38</v>
       </c>
-      <c r="H58" t="s">
-        <v>29</v>
+      <c r="H58" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J58" s="10">
         <v>20</v>
       </c>
       <c r="K58" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L58" s="10">
         <v>25</v>
       </c>
-      <c r="M58" t="s">
-        <v>68</v>
+      <c r="M58" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>9</v>
       </c>
       <c r="N58" t="s">
+        <v>63</v>
+      </c>
+      <c r="O58" t="s">
         <v>33</v>
       </c>
-      <c r="O58" s="13" t="s">
-        <v>129</v>
-      </c>
       <c r="P58" s="13" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="Q58" s="13" t="s">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="R58" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="S58" s="15">
-        <v>0</v>
+        <v>157</v>
+      </c>
+      <c r="S58" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="T58" s="15">
         <v>0</v>
@@ -5840,23 +6063,26 @@
         <v>0</v>
       </c>
       <c r="V58" s="15">
-        <v>1</v>
-      </c>
-      <c r="W58" s="9">
-        <v>1</v>
-      </c>
-      <c r="X58" s="10">
+        <v>0</v>
+      </c>
+      <c r="W58" s="15">
+        <v>1</v>
+      </c>
+      <c r="X58" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="10">
         <v>10</v>
       </c>
-      <c r="Y58" s="10">
+      <c r="Z58" s="10">
         <v>8</v>
       </c>
-      <c r="Z58" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA58" s="10">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>65</v>
       </c>
@@ -5873,71 +6099,75 @@
         <v>17</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G59" t="s">
         <v>38</v>
       </c>
-      <c r="H59" t="s">
-        <v>103</v>
+      <c r="H59" s="24" t="s">
+        <v>177</v>
       </c>
       <c r="I59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J59" s="10">
         <v>8</v>
       </c>
       <c r="K59" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="L59" s="10">
         <v>18</v>
       </c>
-      <c r="M59" t="s">
+      <c r="M59" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>1</v>
+      </c>
+      <c r="N59" t="s">
         <v>32</v>
       </c>
-      <c r="N59" t="s">
-        <v>62</v>
-      </c>
-      <c r="O59" s="13" t="s">
-        <v>63</v>
+      <c r="O59" t="s">
+        <v>57</v>
       </c>
       <c r="P59" s="13" t="s">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="Q59" s="13" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="R59" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S59" s="15">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="S59" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T59" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U59" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" s="15">
         <v>0</v>
       </c>
-      <c r="W59" s="9">
-        <v>1</v>
-      </c>
-      <c r="X59" s="10">
-        <v>8</v>
+      <c r="W59" s="15">
+        <v>0</v>
+      </c>
+      <c r="X59" s="9">
+        <v>1</v>
       </c>
       <c r="Y59" s="10">
         <v>8</v>
       </c>
       <c r="Z59" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="AA59" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>34</v>
       </c>
@@ -5954,46 +6184,47 @@
         <v>16</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G60" t="s">
         <v>38</v>
       </c>
-      <c r="H60" t="s">
-        <v>57</v>
+      <c r="H60" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J60" s="10">
         <v>25</v>
       </c>
       <c r="K60" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L60" s="10">
         <v>24</v>
       </c>
-      <c r="M60" t="s">
-        <v>174</v>
+      <c r="M60" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>8</v>
       </c>
       <c r="N60" t="s">
-        <v>62</v>
-      </c>
-      <c r="O60" s="13" t="s">
-        <v>81</v>
+        <v>159</v>
+      </c>
+      <c r="O60" t="s">
+        <v>57</v>
       </c>
       <c r="P60" s="13" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="Q60" s="13" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="R60" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="S60" s="15">
-        <v>0</v>
+        <v>74</v>
+      </c>
+      <c r="S60" s="13" t="s">
+        <v>161</v>
       </c>
       <c r="T60" s="15">
         <v>0</v>
@@ -6004,21 +6235,24 @@
       <c r="V60" s="15">
         <v>0</v>
       </c>
-      <c r="W60" s="9">
-        <v>1</v>
-      </c>
-      <c r="X60" s="10">
+      <c r="W60" s="15">
+        <v>0</v>
+      </c>
+      <c r="X60" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="10">
         <v>5</v>
       </c>
-      <c r="Y60" s="10">
+      <c r="Z60" s="10">
         <v>8</v>
       </c>
-      <c r="Z60" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA60" s="10">
+        <f t="shared" si="1"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>23</v>
       </c>
@@ -6035,71 +6269,75 @@
         <v>16</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G61" t="s">
-        <v>73</v>
-      </c>
-      <c r="H61" t="s">
-        <v>106</v>
+        <v>67</v>
+      </c>
+      <c r="H61" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I61" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J61" s="10">
         <v>20</v>
       </c>
       <c r="K61" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L61" s="10">
         <v>27</v>
       </c>
-      <c r="M61" t="s">
-        <v>167</v>
+      <c r="M61" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>11</v>
       </c>
       <c r="N61" t="s">
+        <v>153</v>
+      </c>
+      <c r="O61" t="s">
         <v>33</v>
-      </c>
-      <c r="O61" s="13" t="s">
-        <v>44</v>
       </c>
       <c r="P61" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="Q61" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="R61" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="S61" s="15">
-        <v>0</v>
+      <c r="Q61" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="R61" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="S61" s="13" t="s">
+        <v>163</v>
       </c>
       <c r="T61" s="15">
         <v>0</v>
       </c>
-      <c r="U61" s="14">
+      <c r="U61" s="15">
+        <v>0</v>
+      </c>
+      <c r="V61" s="14">
         <v>-1</v>
       </c>
-      <c r="V61" s="15">
-        <v>0</v>
-      </c>
-      <c r="W61" s="9">
-        <v>1</v>
-      </c>
-      <c r="X61" s="10">
+      <c r="W61" s="15">
+        <v>0</v>
+      </c>
+      <c r="X61" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="10">
         <v>5</v>
       </c>
-      <c r="Y61" s="10">
+      <c r="Z61" s="10">
         <v>8</v>
       </c>
-      <c r="Z61" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA61" s="10">
+        <f t="shared" si="1"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>52</v>
       </c>
@@ -6116,46 +6354,47 @@
         <v>16</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G62" t="s">
-        <v>73</v>
-      </c>
-      <c r="H62" t="s">
-        <v>57</v>
+        <v>67</v>
+      </c>
+      <c r="H62" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J62" s="10">
         <v>5</v>
       </c>
       <c r="K62" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L62" s="10">
         <v>19</v>
       </c>
-      <c r="M62" t="s">
-        <v>51</v>
+      <c r="M62" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
       </c>
       <c r="N62" t="s">
+        <v>49</v>
+      </c>
+      <c r="O62" t="s">
         <v>33</v>
       </c>
-      <c r="O62" s="13" t="s">
-        <v>179</v>
-      </c>
       <c r="P62" s="13" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="Q62" s="13" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="R62" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="S62" s="15">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="S62" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="T62" s="15">
         <v>0</v>
@@ -6166,21 +6405,24 @@
       <c r="V62" s="15">
         <v>0</v>
       </c>
-      <c r="W62" s="9">
-        <v>1</v>
-      </c>
-      <c r="X62" s="10">
+      <c r="W62" s="15">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y62" s="10">
         <v>9</v>
       </c>
-      <c r="Y62" s="10">
+      <c r="Z62" s="10">
         <v>12</v>
       </c>
-      <c r="Z62" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA62" s="10">
+        <f t="shared" si="1"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>38</v>
       </c>
@@ -6197,71 +6439,75 @@
         <v>16</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G63" t="s">
         <v>38</v>
       </c>
-      <c r="H63" t="s">
-        <v>57</v>
+      <c r="H63" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I63" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J63" s="10">
         <v>10</v>
       </c>
       <c r="K63" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L63" s="10">
         <v>26</v>
       </c>
-      <c r="M63" t="s">
-        <v>41</v>
+      <c r="M63" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>10</v>
       </c>
       <c r="N63" t="s">
-        <v>170</v>
-      </c>
-      <c r="O63" s="13" t="s">
-        <v>180</v>
+        <v>40</v>
+      </c>
+      <c r="O63" t="s">
+        <v>33</v>
       </c>
       <c r="P63" s="13" t="s">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="Q63" s="13" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="R63" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S63" s="15">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="S63" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T63" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U63" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V63" s="15">
         <v>0</v>
       </c>
-      <c r="W63" s="9">
-        <v>1</v>
-      </c>
-      <c r="X63" s="10">
+      <c r="W63" s="15">
+        <v>0</v>
+      </c>
+      <c r="X63" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y63" s="10">
         <v>4</v>
       </c>
-      <c r="Y63" s="10">
+      <c r="Z63" s="10">
         <v>10</v>
       </c>
-      <c r="Z63" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA63" s="10">
+        <f t="shared" si="1"/>
         <v>-6</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>36</v>
       </c>
@@ -6278,46 +6524,47 @@
         <v>16</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G64" t="s">
         <v>38</v>
       </c>
-      <c r="H64" t="s">
-        <v>39</v>
+      <c r="H64" s="24" t="s">
+        <v>175</v>
       </c>
       <c r="I64" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J64" s="10">
         <v>20</v>
       </c>
       <c r="K64" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L64" s="10">
         <v>65</v>
       </c>
-      <c r="M64" t="s">
+      <c r="M64" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>49</v>
+      </c>
+      <c r="N64" t="s">
         <v>32</v>
       </c>
-      <c r="N64" t="s">
+      <c r="O64" t="s">
         <v>33</v>
       </c>
-      <c r="O64" s="13" t="s">
-        <v>165</v>
-      </c>
       <c r="P64" s="13" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="Q64" s="13" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="R64" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S64" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S64" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T64" s="15">
         <v>0</v>
@@ -6328,21 +6575,24 @@
       <c r="V64" s="15">
         <v>0</v>
       </c>
-      <c r="W64" s="9">
-        <v>1</v>
-      </c>
-      <c r="X64" s="10">
+      <c r="W64" s="15">
+        <v>0</v>
+      </c>
+      <c r="X64" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y64" s="10">
         <v>8</v>
       </c>
-      <c r="Y64" s="10">
+      <c r="Z64" s="10">
         <v>5</v>
       </c>
-      <c r="Z64" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA64" s="10">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>30</v>
       </c>
@@ -6359,46 +6609,47 @@
         <v>16</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G65" t="s">
         <v>38</v>
       </c>
-      <c r="H65" t="s">
-        <v>57</v>
+      <c r="H65" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J65" s="10">
         <v>20</v>
       </c>
       <c r="K65" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L65" s="10">
         <v>25</v>
       </c>
-      <c r="M65" t="s">
-        <v>41</v>
+      <c r="M65" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>9</v>
       </c>
       <c r="N65" t="s">
-        <v>62</v>
-      </c>
-      <c r="O65" s="13" t="s">
-        <v>63</v>
+        <v>40</v>
+      </c>
+      <c r="O65" t="s">
+        <v>57</v>
       </c>
       <c r="P65" s="13" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="Q65" s="13" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="R65" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S65" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S65" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T65" s="15">
         <v>0</v>
@@ -6409,21 +6660,24 @@
       <c r="V65" s="15">
         <v>0</v>
       </c>
-      <c r="W65" s="9">
-        <v>1</v>
-      </c>
-      <c r="X65" s="10">
-        <v>4</v>
+      <c r="W65" s="15">
+        <v>0</v>
+      </c>
+      <c r="X65" s="9">
+        <v>1</v>
       </c>
       <c r="Y65" s="10">
         <v>4</v>
       </c>
       <c r="Z65" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="AA65" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>71</v>
       </c>
@@ -6440,71 +6694,75 @@
         <v>16</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G66" t="s">
         <v>38</v>
       </c>
-      <c r="H66" t="s">
-        <v>29</v>
+      <c r="H66" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J66" s="10">
         <v>10</v>
       </c>
       <c r="K66" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L66" s="10">
         <v>28</v>
       </c>
-      <c r="M66" t="s">
-        <v>68</v>
+      <c r="M66" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>12</v>
       </c>
       <c r="N66" t="s">
-        <v>62</v>
-      </c>
-      <c r="O66" s="13" t="s">
-        <v>182</v>
+        <v>63</v>
+      </c>
+      <c r="O66" t="s">
+        <v>57</v>
       </c>
       <c r="P66" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q66" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="R66" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="Q66" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="R66" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="S66" s="15">
+      <c r="S66" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="T66" s="15">
         <v>2</v>
       </c>
-      <c r="T66" s="15">
-        <v>0</v>
-      </c>
       <c r="U66" s="15">
         <v>0</v>
       </c>
       <c r="V66" s="15">
         <v>0</v>
       </c>
-      <c r="W66" s="9">
-        <v>1</v>
-      </c>
-      <c r="X66" s="10">
+      <c r="W66" s="15">
+        <v>0</v>
+      </c>
+      <c r="X66" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y66" s="10">
         <v>5</v>
       </c>
-      <c r="Y66" s="10">
+      <c r="Z66" s="10">
         <v>17</v>
       </c>
-      <c r="Z66" s="10">
-        <f t="shared" si="0"/>
+      <c r="AA66" s="10">
+        <f t="shared" ref="AA66:AA71" si="2">Y66-Z66</f>
         <v>-12</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>32</v>
       </c>
@@ -6521,71 +6779,75 @@
         <v>16</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G67" t="s">
         <v>38</v>
       </c>
-      <c r="H67" t="s">
-        <v>57</v>
+      <c r="H67" s="24" t="s">
+        <v>176</v>
       </c>
       <c r="I67" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J67" s="10">
         <v>60</v>
       </c>
       <c r="K67" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L67" s="10">
         <v>22</v>
       </c>
-      <c r="M67" t="s">
-        <v>107</v>
+      <c r="M67" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>6</v>
       </c>
       <c r="N67" t="s">
+        <v>95</v>
+      </c>
+      <c r="O67" t="s">
         <v>33</v>
       </c>
-      <c r="O67" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="P67" s="13" t="s">
-        <v>43</v>
+      <c r="P67" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="Q67" s="13" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="R67" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="S67" s="14">
+        <v>97</v>
+      </c>
+      <c r="S67" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="T67" s="14">
         <v>-1</v>
       </c>
-      <c r="T67" s="15">
-        <v>0</v>
-      </c>
       <c r="U67" s="15">
         <v>0</v>
       </c>
       <c r="V67" s="15">
         <v>0</v>
       </c>
-      <c r="W67" s="9">
-        <v>1</v>
-      </c>
-      <c r="X67" s="10">
+      <c r="W67" s="15">
+        <v>0</v>
+      </c>
+      <c r="X67" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y67" s="10">
         <v>7</v>
       </c>
-      <c r="Y67" s="10">
+      <c r="Z67" s="10">
         <v>13</v>
       </c>
-      <c r="Z67" s="10">
-        <f t="shared" ref="Z67:Z74" si="1">X67-Y67</f>
+      <c r="AA67" s="10">
+        <f t="shared" si="2"/>
         <v>-6</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>18</v>
       </c>
@@ -6602,71 +6864,75 @@
         <v>16</v>
       </c>
       <c r="F68" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G68" t="s">
+        <v>46</v>
+      </c>
+      <c r="H68" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I68" t="s">
         <v>72</v>
-      </c>
-      <c r="G68" t="s">
-        <v>47</v>
-      </c>
-      <c r="H68" t="s">
-        <v>106</v>
-      </c>
-      <c r="I68" t="s">
-        <v>79</v>
       </c>
       <c r="J68" s="10">
         <v>35</v>
       </c>
       <c r="K68" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="L68" s="10">
         <v>19</v>
       </c>
-      <c r="M68" t="s">
-        <v>51</v>
+      <c r="M68" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
       </c>
       <c r="N68" t="s">
+        <v>49</v>
+      </c>
+      <c r="O68" t="s">
         <v>33</v>
       </c>
-      <c r="O68" s="13" t="s">
-        <v>42</v>
-      </c>
       <c r="P68" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q68" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q68" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="R68" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="R68" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="S68" s="15">
-        <v>0</v>
+      <c r="S68" s="13" t="s">
+        <v>96</v>
       </c>
       <c r="T68" s="15">
         <v>0</v>
       </c>
-      <c r="U68" s="14">
+      <c r="U68" s="15">
+        <v>0</v>
+      </c>
+      <c r="V68" s="14">
         <v>-1</v>
       </c>
-      <c r="V68" s="15">
+      <c r="W68" s="15">
         <v>2</v>
       </c>
-      <c r="W68" s="9">
-        <v>1</v>
-      </c>
-      <c r="X68" s="10">
+      <c r="X68" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y68" s="10">
         <v>8</v>
       </c>
-      <c r="Y68" s="9">
+      <c r="Z68" s="9">
         <v>11</v>
       </c>
-      <c r="Z68" s="10">
-        <f t="shared" si="1"/>
+      <c r="AA68" s="10">
+        <f t="shared" si="2"/>
         <v>-3</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>47</v>
       </c>
@@ -6683,71 +6949,75 @@
         <v>17</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G69" t="s">
-        <v>67</v>
-      </c>
-      <c r="H69" t="s">
-        <v>29</v>
+        <v>62</v>
+      </c>
+      <c r="H69" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J69" s="10">
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L69" s="10">
         <v>24</v>
       </c>
-      <c r="M69" t="s">
-        <v>68</v>
+      <c r="M69" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>7</v>
       </c>
       <c r="N69" t="s">
+        <v>63</v>
+      </c>
+      <c r="O69" t="s">
         <v>33</v>
       </c>
-      <c r="O69" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="P69" s="13" t="s">
-        <v>183</v>
+        <v>58</v>
       </c>
       <c r="Q69" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="R69" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="S69" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="R69" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S69" s="15">
-        <v>0</v>
-      </c>
       <c r="T69" s="15">
+        <v>0</v>
+      </c>
+      <c r="U69" s="15">
         <v>2</v>
       </c>
-      <c r="U69" s="15">
-        <v>0</v>
-      </c>
       <c r="V69" s="15">
         <v>0</v>
       </c>
       <c r="W69" s="15">
-        <v>1</v>
-      </c>
-      <c r="X69" s="10">
+        <v>0</v>
+      </c>
+      <c r="X69" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y69" s="10">
         <v>5</v>
       </c>
-      <c r="Y69" s="10">
+      <c r="Z69" s="10">
         <v>6</v>
       </c>
-      <c r="Z69" s="10">
-        <f t="shared" si="1"/>
+      <c r="AA69" s="10">
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>10</v>
       </c>
@@ -6764,74 +7034,78 @@
         <v>16</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G70" t="s">
-        <v>184</v>
-      </c>
-      <c r="H70" t="s">
-        <v>48</v>
+        <v>169</v>
+      </c>
+      <c r="H70" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="I70" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J70" s="10">
         <v>20</v>
       </c>
       <c r="K70" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L70" s="10">
         <v>24</v>
       </c>
-      <c r="M70" t="s">
-        <v>107</v>
+      <c r="M70" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>8</v>
       </c>
       <c r="N70" t="s">
+        <v>95</v>
+      </c>
+      <c r="O70" t="s">
         <v>33</v>
       </c>
-      <c r="O70" s="13" t="s">
-        <v>44</v>
-      </c>
       <c r="P70" s="13" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="Q70" s="13" t="s">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c r="R70" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S70" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S70" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="T70" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U70" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V70" s="15">
         <v>0</v>
       </c>
-      <c r="W70" s="9">
-        <v>1</v>
-      </c>
-      <c r="X70" s="10">
+      <c r="W70" s="15">
+        <v>0</v>
+      </c>
+      <c r="X70" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y70" s="10">
         <v>3</v>
       </c>
-      <c r="Y70" s="9">
+      <c r="Z70" s="9">
         <v>15</v>
       </c>
-      <c r="Z70" s="10">
-        <f t="shared" si="1"/>
+      <c r="AA70" s="10">
+        <f t="shared" si="2"/>
         <v>-12</v>
       </c>
-      <c r="AA70" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="71" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB70" s="16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>24</v>
       </c>
@@ -6848,438 +7122,205 @@
         <v>17</v>
       </c>
       <c r="F71" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71" t="s">
+        <v>67</v>
+      </c>
+      <c r="H71" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I71" t="s">
         <v>72</v>
-      </c>
-      <c r="G71" t="s">
-        <v>73</v>
-      </c>
-      <c r="H71" t="s">
-        <v>106</v>
-      </c>
-      <c r="I71" t="s">
-        <v>79</v>
       </c>
       <c r="J71" s="10">
         <v>50</v>
       </c>
       <c r="K71" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="L71" s="10">
         <v>20</v>
       </c>
-      <c r="M71" t="s">
-        <v>51</v>
+      <c r="M71" s="10">
+        <f>Table1[[#This Row],[CurrentAge]]-Table1[[#This Row],[AgeStart]]</f>
+        <v>3</v>
       </c>
       <c r="N71" t="s">
-        <v>62</v>
-      </c>
-      <c r="O71" s="13" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="O71" t="s">
+        <v>57</v>
       </c>
       <c r="P71" s="13" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="Q71" s="13" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="R71" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="S71" s="15">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="S71" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="T71" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U71" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V71" s="15">
-        <v>1</v>
-      </c>
-      <c r="W71" s="9">
-        <v>1</v>
-      </c>
-      <c r="X71" s="10">
+        <v>0</v>
+      </c>
+      <c r="W71" s="15">
+        <v>1</v>
+      </c>
+      <c r="X71" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y71" s="10">
         <v>6</v>
       </c>
-      <c r="Y71" s="10">
+      <c r="Z71" s="10">
         <v>10</v>
       </c>
-      <c r="Z71" s="10">
-        <f t="shared" si="1"/>
+      <c r="AA71" s="10">
+        <f t="shared" si="2"/>
         <v>-4</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>66</v>
-      </c>
-      <c r="B72" s="9">
-        <v>3</v>
-      </c>
-      <c r="C72" s="9">
-        <v>70</v>
-      </c>
-      <c r="D72" s="1">
-        <v>97051</v>
-      </c>
-      <c r="E72" s="10">
-        <v>16</v>
-      </c>
-      <c r="F72" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G72" t="s">
-        <v>38</v>
-      </c>
-      <c r="H72" t="s">
-        <v>39</v>
-      </c>
-      <c r="I72" t="s">
-        <v>40</v>
-      </c>
-      <c r="J72" s="10">
-        <v>3</v>
-      </c>
-      <c r="K72" t="s">
-        <v>31</v>
-      </c>
-      <c r="L72" s="10">
-        <v>24</v>
-      </c>
-      <c r="M72" t="s">
-        <v>68</v>
-      </c>
-      <c r="N72" t="s">
-        <v>62</v>
-      </c>
-      <c r="O72" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="P72" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q72" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="R72" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="S72" s="15">
-        <v>0</v>
-      </c>
-      <c r="T72" s="15">
-        <v>1</v>
-      </c>
-      <c r="U72" s="15">
-        <v>0</v>
-      </c>
-      <c r="V72" s="15">
-        <v>1</v>
-      </c>
-      <c r="W72" s="9">
-        <v>1</v>
-      </c>
-      <c r="X72" s="10">
-        <v>9</v>
-      </c>
-      <c r="Y72" s="10">
-        <v>7</v>
-      </c>
-      <c r="Z72" s="10">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>27</v>
-      </c>
-      <c r="B73" s="9">
-        <v>1</v>
-      </c>
-      <c r="C73" s="9">
-        <v>71</v>
-      </c>
-      <c r="D73" s="1">
-        <v>97448</v>
-      </c>
-      <c r="E73" s="10">
-        <v>18</v>
-      </c>
-      <c r="F73" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G73" t="s">
-        <v>161</v>
-      </c>
-      <c r="H73" t="s">
-        <v>29</v>
-      </c>
-      <c r="I73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J73" s="10">
-        <v>45</v>
-      </c>
-      <c r="K73" t="s">
-        <v>31</v>
-      </c>
-      <c r="L73" s="10">
-        <v>18</v>
-      </c>
-      <c r="M73" t="s">
-        <v>32</v>
-      </c>
-      <c r="N73" t="s">
-        <v>33</v>
-      </c>
-      <c r="O73" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="P73" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q73" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="R73" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="S73" s="15">
-        <v>0</v>
-      </c>
-      <c r="T73" s="15">
-        <v>0</v>
-      </c>
-      <c r="U73" s="15">
-        <v>0</v>
-      </c>
-      <c r="V73" s="15">
-        <v>0</v>
-      </c>
-      <c r="W73" s="9">
-        <v>1</v>
-      </c>
-      <c r="X73" s="10">
-        <v>6</v>
-      </c>
-      <c r="Y73" s="10">
-        <v>13</v>
-      </c>
-      <c r="Z73" s="10">
-        <f t="shared" si="1"/>
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>13</v>
-      </c>
-      <c r="B74" s="9">
-        <v>0</v>
-      </c>
-      <c r="C74" s="9">
-        <v>72</v>
-      </c>
-      <c r="D74" s="1">
-        <v>97973</v>
-      </c>
-      <c r="E74" s="10">
-        <v>16</v>
-      </c>
-      <c r="F74" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G74" t="s">
-        <v>153</v>
-      </c>
-      <c r="H74" t="s">
-        <v>114</v>
-      </c>
-      <c r="I74" t="s">
-        <v>49</v>
-      </c>
-      <c r="J74" s="10">
-        <v>15</v>
-      </c>
-      <c r="K74" t="s">
-        <v>50</v>
-      </c>
-      <c r="L74" s="10">
-        <v>21</v>
-      </c>
-      <c r="M74" t="s">
-        <v>51</v>
-      </c>
-      <c r="N74" t="s">
-        <v>33</v>
-      </c>
-      <c r="O74" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="P74" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q74" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="R74" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="S74" s="15">
-        <v>0</v>
-      </c>
-      <c r="T74" s="15">
-        <v>0</v>
-      </c>
-      <c r="U74" s="15">
-        <v>0</v>
-      </c>
-      <c r="V74" s="15">
-        <v>0</v>
-      </c>
-      <c r="W74" s="9">
-        <v>1</v>
-      </c>
-      <c r="X74" s="10">
-        <v>5</v>
-      </c>
-      <c r="Y74" s="9">
-        <v>10</v>
-      </c>
-      <c r="Z74" s="10">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="L72" s="18"/>
+      <c r="M72" s="18"/>
+      <c r="P72" s="13"/>
+      <c r="Q72" s="13"/>
+      <c r="R72" s="13"/>
+      <c r="S72" s="13"/>
+      <c r="T72" s="19"/>
+      <c r="U72" s="19"/>
+      <c r="V72" s="19"/>
+      <c r="W72" s="19"/>
+      <c r="X72" s="17"/>
+      <c r="Y72" s="18"/>
+      <c r="Z72" s="18"/>
+      <c r="AA72" s="18"/>
+    </row>
+    <row r="73" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18"/>
+      <c r="P73" s="13"/>
+      <c r="Q73" s="13"/>
+      <c r="R73" s="13"/>
+      <c r="S73" s="13"/>
+      <c r="T73" s="19"/>
+      <c r="U73" s="19"/>
+      <c r="V73" s="19"/>
+      <c r="W73" s="19"/>
+      <c r="X73" s="17"/>
+      <c r="Y73" s="18"/>
+      <c r="Z73" s="18"/>
+      <c r="AA73" s="18"/>
+    </row>
+    <row r="74" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="L74" s="18"/>
+      <c r="M74" s="18"/>
+      <c r="P74" s="13"/>
+      <c r="Q74" s="13"/>
+      <c r="R74" s="13"/>
+      <c r="S74" s="13"/>
+      <c r="T74" s="19"/>
+      <c r="U74" s="19"/>
+      <c r="V74" s="19"/>
+      <c r="W74" s="19"/>
+      <c r="X74" s="17"/>
+      <c r="Y74" s="18"/>
+      <c r="Z74" s="18"/>
+      <c r="AA74" s="18"/>
+    </row>
+    <row r="75" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
       <c r="D75" s="1"/>
-      <c r="E75" s="17"/>
-      <c r="J75" s="17"/>
-      <c r="L75" s="17"/>
-      <c r="O75" s="13"/>
+      <c r="E75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="L75" s="18"/>
+      <c r="M75" s="18"/>
       <c r="P75" s="13"/>
       <c r="Q75" s="13"/>
       <c r="R75" s="13"/>
-      <c r="S75" s="18"/>
-      <c r="T75" s="18"/>
-      <c r="U75" s="18"/>
-      <c r="V75" s="18"/>
-      <c r="W75" s="16"/>
+      <c r="S75" s="13"/>
+      <c r="T75" s="19"/>
+      <c r="U75" s="19"/>
+      <c r="V75" s="19"/>
+      <c r="W75" s="19"/>
       <c r="X75" s="17"/>
-      <c r="Y75" s="17"/>
-      <c r="Z75" s="17"/>
-    </row>
-    <row r="76" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y75" s="18"/>
+      <c r="Z75" s="18"/>
+      <c r="AA75" s="18"/>
+    </row>
+    <row r="76" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
       <c r="D76" s="1"/>
-      <c r="E76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="L76" s="17"/>
-      <c r="O76" s="13"/>
+      <c r="E76" s="18"/>
+      <c r="J76" s="18"/>
+      <c r="L76" s="18"/>
+      <c r="M76" s="18"/>
       <c r="P76" s="13"/>
       <c r="Q76" s="13"/>
       <c r="R76" s="13"/>
-      <c r="S76" s="18"/>
-      <c r="T76" s="18"/>
-      <c r="U76" s="18"/>
-      <c r="V76" s="18"/>
-      <c r="W76" s="16"/>
+      <c r="S76" s="13"/>
+      <c r="T76" s="19"/>
+      <c r="U76" s="19"/>
+      <c r="V76" s="19"/>
+      <c r="W76" s="19"/>
       <c r="X76" s="17"/>
-      <c r="Y76" s="17"/>
-      <c r="Z76" s="17"/>
-    </row>
-    <row r="77" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y76" s="18"/>
+      <c r="Z76" s="18"/>
+      <c r="AA76" s="18"/>
+    </row>
+    <row r="77" spans="1:28" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="17"/>
       <c r="D77" s="1"/>
-      <c r="E77" s="17"/>
-      <c r="J77" s="17"/>
-      <c r="L77" s="17"/>
-      <c r="O77" s="13"/>
+      <c r="E77" s="18"/>
+      <c r="J77" s="18"/>
+      <c r="L77" s="18"/>
+      <c r="M77" s="18"/>
       <c r="P77" s="13"/>
       <c r="Q77" s="13"/>
       <c r="R77" s="13"/>
-      <c r="S77" s="18"/>
-      <c r="T77" s="18"/>
-      <c r="U77" s="18"/>
-      <c r="V77" s="18"/>
-      <c r="W77" s="16"/>
+      <c r="S77" s="13"/>
+      <c r="T77" s="19"/>
+      <c r="U77" s="19"/>
+      <c r="V77" s="19"/>
+      <c r="W77" s="19"/>
       <c r="X77" s="17"/>
-      <c r="Y77" s="17"/>
-      <c r="Z77" s="17"/>
-    </row>
-    <row r="78" spans="1:27" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="17"/>
-      <c r="J78" s="17"/>
-      <c r="L78" s="17"/>
-      <c r="O78" s="13"/>
-      <c r="P78" s="13"/>
-      <c r="Q78" s="13"/>
-      <c r="R78" s="13"/>
-      <c r="S78" s="18"/>
-      <c r="T78" s="18"/>
-      <c r="U78" s="18"/>
-      <c r="V78" s="18"/>
-      <c r="W78" s="16"/>
-      <c r="X78" s="17"/>
-      <c r="Y78" s="17"/>
-      <c r="Z78" s="17"/>
-    </row>
-    <row r="79" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1"/>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="17"/>
-      <c r="J79" s="17"/>
-      <c r="L79" s="17"/>
-      <c r="O79" s="13"/>
-      <c r="P79" s="13"/>
-      <c r="Q79" s="13"/>
-      <c r="R79" s="13"/>
-      <c r="S79" s="18"/>
-      <c r="T79" s="18"/>
-      <c r="U79" s="18"/>
-      <c r="V79" s="18"/>
-      <c r="W79" s="16"/>
-      <c r="X79" s="17"/>
-      <c r="Y79" s="17"/>
-      <c r="Z79" s="17"/>
-    </row>
-    <row r="80" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="B80" s="16"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="L80" s="17"/>
-      <c r="O80" s="13"/>
-      <c r="P80" s="13"/>
-      <c r="Q80" s="13"/>
-      <c r="R80" s="13"/>
-      <c r="S80" s="18"/>
-      <c r="T80" s="18"/>
-      <c r="U80" s="18"/>
-      <c r="V80" s="18"/>
-      <c r="W80" s="16"/>
-      <c r="X80" s="17"/>
-      <c r="Y80" s="17"/>
-      <c r="Z80" s="17"/>
+      <c r="Y77" s="18"/>
+      <c r="Z77" s="18"/>
+      <c r="AA77" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
